--- a/PRIZEPICKS_HITTER_AI_V5_TOP30_2026_07_23.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V5_TOP30_2026_07_23.xlsx
@@ -2130,10 +2130,10 @@
         <v>12.12</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>11.29</v>
+        <v>11.31</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>11.29</v>
+        <v>11.31</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>9.17</v>
@@ -2151,7 +2151,7 @@
         <v>8.23</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.925</v>
+        <v>0.926</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>9.4</v>
@@ -2187,31 +2187,31 @@
         <v>91.8</v>
       </c>
       <c r="AB2" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="AD2" s="5" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="AE2" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="AF2" s="5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="AG2" s="5" t="n">
-        <v>67.8</v>
+        <v>68</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>67.3</v>
+        <v>67.5</v>
       </c>
       <c r="AI2" s="5" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
       <c r="AJ2" s="5" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="AK2" s="6" t="n">
         <v>52.6</v>
@@ -2220,19 +2220,19 @@
         <v>52.6</v>
       </c>
       <c r="AM2" s="7" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="AN2" s="7" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="AO2" s="7" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="AP2" s="7" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="AQ2" s="8" t="n">
-        <v>39.9</v>
+        <v>42.9</v>
+      </c>
+      <c r="AQ2" s="7" t="n">
+        <v>40</v>
       </c>
       <c r="AR2" s="8" t="n">
         <v>36.4</v>
@@ -2247,19 +2247,19 @@
         <v>34.4</v>
       </c>
       <c r="AV2" s="8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="AW2" s="8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="AX2" s="8" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="AY2" s="8" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="AZ2" s="3" t="n">
-        <v>274.53</v>
+        <v>274.86</v>
       </c>
       <c r="BA2" s="4" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="BB2" s="9" t="inlineStr">
         <is>
-          <t>MORE 8.0 | 58.2% | Edge +3.3</t>
+          <t>MORE 8.0 | 58.4% | Edge +3.3</t>
         </is>
       </c>
       <c r="BC2" s="4" t="inlineStr">
@@ -2280,13 +2280,13 @@
         <v>8</v>
       </c>
       <c r="BE2" s="3" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="BF2" s="3" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="BG2" s="3" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="BH2" s="4" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>5.47</v>
       </c>
       <c r="GT2" s="3" t="n">
-        <v>16.57</v>
+        <v>16.58</v>
       </c>
       <c r="GU2" s="3" t="n">
         <v>22.13</v>
@@ -2769,31 +2769,31 @@
         <v>86.8</v>
       </c>
       <c r="HB2" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="HC2" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="HD2" s="3" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="HE2" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="HF2" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="HG2" s="3" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="HH2" s="3" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="HI2" s="3" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="HJ2" s="3" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="HK2" s="3" t="n">
         <v>52.6</v>
@@ -2802,19 +2802,19 @@
         <v>52.6</v>
       </c>
       <c r="HM2" s="3" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="HN2" s="3" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="HO2" s="3" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="HP2" s="3" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="HQ2" s="3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="HR2" s="3" t="n">
         <v>36.4</v>
@@ -2829,16 +2829,16 @@
         <v>34.4</v>
       </c>
       <c r="HV2" s="3" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="HW2" s="3" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="HX2" s="3" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="HY2" s="3" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="HZ2" s="3" t="n">
         <v>2.9</v>
@@ -3226,13 +3226,13 @@
         <v>1.03</v>
       </c>
       <c r="CI3" s="3" t="n">
-        <v>85.2</v>
+        <v>86.3</v>
       </c>
       <c r="CJ3" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="CK3" s="3" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="CL3" s="3" t="n">
         <v>3</v>
@@ -3467,7 +3467,7 @@
         <v>16.4</v>
       </c>
       <c r="FF3" s="3" t="n">
-        <v>1.0291</v>
+        <v>1.029</v>
       </c>
       <c r="FG3" s="3" t="n">
         <v>1.0024</v>
@@ -4078,13 +4078,13 @@
         <v>1.03</v>
       </c>
       <c r="CI4" s="3" t="n">
-        <v>85.2</v>
+        <v>86.3</v>
       </c>
       <c r="CJ4" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="CK4" s="3" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="CL4" s="3" t="n">
         <v>3</v>
@@ -4678,10 +4678,10 @@
         <v>10.09</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>9.16</v>
+        <v>9.18</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>9.16</v>
+        <v>9.18</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>7.39</v>
@@ -4693,7 +4693,7 @@
         <v>6.11</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>7.44</v>
+        <v>7.45</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>6.11</v>
@@ -4738,46 +4738,46 @@
         <v>89.3</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AD5" s="5" t="n">
-        <v>76.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="AJ5" s="7" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="AK5" s="7" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="AL5" s="7" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="AM5" s="8" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="AN5" s="8" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="AO5" s="8" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="AP5" s="8" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="AQ5" s="8" t="n">
         <v>26.2</v>
@@ -4786,10 +4786,10 @@
         <v>26.2</v>
       </c>
       <c r="AS5" s="8" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="AT5" s="8" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="AU5" s="8" t="n">
         <v>20.1</v>
@@ -4801,13 +4801,13 @@
         <v>18.5</v>
       </c>
       <c r="AX5" s="8" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="AY5" s="8" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="AZ5" s="3" t="n">
-        <v>231.77</v>
+        <v>232.1</v>
       </c>
       <c r="BA5" s="4" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="BB5" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.0 | 60.5% | Edge +2.2</t>
+          <t>MORE 7.0 | 60.6% | Edge +2.2</t>
         </is>
       </c>
       <c r="BC5" s="4" t="inlineStr">
@@ -4828,13 +4828,13 @@
         <v>7</v>
       </c>
       <c r="BE5" s="3" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="BF5" s="3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BG5" s="3" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="BH5" s="4" t="inlineStr">
         <is>
@@ -5288,13 +5288,13 @@
         <v>6.11</v>
       </c>
       <c r="GS5" s="3" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="GT5" s="3" t="n">
         <v>12.31</v>
       </c>
       <c r="GU5" s="3" t="n">
-        <v>17.24</v>
+        <v>17.32</v>
       </c>
       <c r="GV5" s="3" t="n">
         <v>4.68</v>
@@ -5320,46 +5320,46 @@
         <v>83.59999999999999</v>
       </c>
       <c r="HC5" s="3" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="HD5" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="HE5" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="HF5" s="3" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
       <c r="HG5" s="3" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
       <c r="HH5" s="3" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="HI5" s="3" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="HJ5" s="3" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="HK5" s="3" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="HL5" s="3" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="HM5" s="3" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="HN5" s="3" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="HO5" s="3" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="HP5" s="3" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="HQ5" s="3" t="n">
         <v>26.2</v>
@@ -5368,10 +5368,10 @@
         <v>26.2</v>
       </c>
       <c r="HS5" s="3" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="HT5" s="3" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="HU5" s="3" t="n">
         <v>20.1</v>
@@ -5383,10 +5383,10 @@
         <v>18.5</v>
       </c>
       <c r="HX5" s="3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="HY5" s="3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="HZ5" s="3" t="n">
         <v>4.3</v>
@@ -5774,13 +5774,13 @@
         <v>1.03</v>
       </c>
       <c r="CI6" s="3" t="n">
-        <v>85.2</v>
+        <v>86.3</v>
       </c>
       <c r="CJ6" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="CK6" s="3" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="CL6" s="3" t="n">
         <v>3</v>
@@ -6374,13 +6374,13 @@
         <v>9.83</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>7.4</v>
+        <v>7.39</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>6.19</v>
@@ -6389,7 +6389,7 @@
         <v>6.12</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>6.12</v>
@@ -6422,64 +6422,64 @@
         </is>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="AA7" s="5" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="AB7" s="5" t="n">
         <v>88</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="AG7" s="5" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="AJ7" s="7" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="AK7" s="7" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="AL7" s="7" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="AM7" s="8" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="AO7" s="8" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="AP7" s="8" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="AQ7" s="8" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="AR7" s="8" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="AS7" s="8" t="n">
         <v>24.3</v>
@@ -6488,7 +6488,7 @@
         <v>24.3</v>
       </c>
       <c r="AU7" s="8" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AV7" s="8" t="n">
         <v>19.2</v>
@@ -6497,13 +6497,13 @@
         <v>19.2</v>
       </c>
       <c r="AX7" s="8" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="AY7" s="8" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="AZ7" s="3" t="n">
-        <v>225.5</v>
+        <v>225.32</v>
       </c>
       <c r="BA7" s="4" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="BB7" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.0 | 58.5% | Edge +2.1</t>
+          <t>MORE 7.0 | 58.4% | Edge +2.1</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
@@ -6524,13 +6524,13 @@
         <v>7</v>
       </c>
       <c r="BE7" s="3" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="BF7" s="3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BG7" s="3" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="BH7" s="4" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>6.12</v>
       </c>
       <c r="GS7" s="3" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="GT7" s="3" t="n">
         <v>12.24</v>
@@ -7004,64 +7004,64 @@
         </is>
       </c>
       <c r="GY7" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="GZ7" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="HA7" s="3" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="HB7" s="3" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="HC7" s="3" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="HD7" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="HE7" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="HF7" s="3" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="HG7" s="3" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="HH7" s="3" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="HI7" s="3" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="HJ7" s="3" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="HK7" s="3" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="HL7" s="3" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="HM7" s="3" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="HN7" s="3" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="HO7" s="3" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="HP7" s="3" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="HQ7" s="3" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="HR7" s="3" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="HS7" s="3" t="n">
         <v>24.3</v>
@@ -7070,7 +7070,7 @@
         <v>24.3</v>
       </c>
       <c r="HU7" s="3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="HV7" s="3" t="n">
         <v>19.2</v>
@@ -7079,22 +7079,22 @@
         <v>19.2</v>
       </c>
       <c r="HX7" s="3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="HY7" s="3" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="HZ7" s="3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="IA7" s="3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="IB7" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="IC7" s="3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="ID7" s="3" t="n">
         <v>6</v>
@@ -7233,13 +7233,13 @@
         <v>6.78</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>6.78</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.869</v>
+        <v>0.868</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>15</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>89.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="Z8" s="5" t="n">
         <v>81.7</v>
@@ -7284,10 +7284,10 @@
         <v>65.8</v>
       </c>
       <c r="AE8" s="6" t="n">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
       <c r="AF8" s="7" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="AG8" s="7" t="n">
         <v>51</v>
@@ -7296,10 +7296,10 @@
         <v>50.5</v>
       </c>
       <c r="AI8" s="7" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="AJ8" s="7" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>36.9</v>
@@ -7338,7 +7338,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" s="8" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AX8" s="8" t="n">
         <v>15.2</v>
@@ -7347,7 +7347,7 @@
         <v>15.2</v>
       </c>
       <c r="AZ8" s="3" t="n">
-        <v>215.73</v>
+        <v>215.74</v>
       </c>
       <c r="BA8" s="4" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>11.5</v>
       </c>
       <c r="GU8" s="3" t="n">
-        <v>17.58</v>
+        <v>17.57</v>
       </c>
       <c r="GV8" s="3" t="n">
         <v>4.44</v>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="GY8" s="3" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="GZ8" s="3" t="n">
         <v>73.7</v>
@@ -7874,10 +7874,10 @@
         <v>60.8</v>
       </c>
       <c r="HE8" s="3" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="HF8" s="3" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="HG8" s="3" t="n">
         <v>47.5</v>
@@ -7886,10 +7886,10 @@
         <v>47.5</v>
       </c>
       <c r="HI8" s="3" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="HJ8" s="3" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="HK8" s="3" t="n">
         <v>36.9</v>
@@ -7928,7 +7928,7 @@
         <v>19.5</v>
       </c>
       <c r="HW8" s="3" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="HX8" s="3" t="n">
         <v>15.2</v>
@@ -8067,16 +8067,16 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.35</v>
+        <v>8.33</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>8.35</v>
+        <v>8.33</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8.789999999999999</v>
@@ -8085,13 +8085,13 @@
         <v>7.86</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.52</v>
+        <v>7.46</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>7.79</v>
+        <v>7.78</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1.046</v>
+        <v>1.053</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>9.4</v>
@@ -8121,28 +8121,28 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Z9" s="5" t="n">
-        <v>76.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AA9" s="5" t="n">
-        <v>75.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AB9" s="5" t="n">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>70.3</v>
+        <v>70.7</v>
       </c>
       <c r="AD9" s="5" t="n">
-        <v>58.5</v>
+        <v>58.8</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="AF9" s="6" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
       <c r="AG9" s="7" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="AH9" s="7" t="n">
         <v>45.4</v>
@@ -8151,55 +8151,55 @@
         <v>44.9</v>
       </c>
       <c r="AJ9" s="8" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="AL9" s="8" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="AM9" s="8" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="AN9" s="8" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="AO9" s="8" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="AP9" s="8" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="AQ9" s="8" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="AR9" s="8" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="AS9" s="8" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="AT9" s="8" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="AU9" s="8" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="AV9" s="8" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="AW9" s="8" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AX9" s="8" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AY9" s="8" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AZ9" s="3" t="n">
-        <v>213.37</v>
+        <v>213.11</v>
       </c>
       <c r="BA9" s="4" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BB9" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.5 | 58.0% | Edge +2.8</t>
+          <t>MORE 5.5 | 58.3% | Edge +2.8</t>
         </is>
       </c>
       <c r="BC9" s="4" t="inlineStr">
@@ -8220,13 +8220,13 @@
         <v>5.5</v>
       </c>
       <c r="BE9" s="3" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="BF9" s="3" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="BG9" s="3" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="BH9" s="4" t="inlineStr">
         <is>
@@ -8322,13 +8322,13 @@
         <v>1</v>
       </c>
       <c r="CI9" s="3" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="CJ9" s="3" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CK9" s="3" t="n">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="CL9" s="3" t="n">
         <v>0</v>
@@ -8457,13 +8457,13 @@
         <v>0</v>
       </c>
       <c r="DX9" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DY9" s="3" t="n">
         <v>10.18</v>
       </c>
       <c r="DZ9" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="EA9" s="3" t="n">
         <v>9.9</v>
@@ -8563,19 +8563,19 @@
         <v>28.1</v>
       </c>
       <c r="FF9" s="3" t="n">
-        <v>0.9786</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="FG9" s="3" t="n">
         <v>1.0001</v>
       </c>
       <c r="FH9" s="3" t="n">
-        <v>0.9791</v>
+        <v>0.9808</v>
       </c>
       <c r="FI9" s="3" t="n">
         <v>1.0003</v>
       </c>
       <c r="FJ9" s="3" t="n">
-        <v>0.9795</v>
+        <v>0.9812</v>
       </c>
       <c r="FK9" s="3" t="n">
         <v>1.0091</v>
@@ -8635,19 +8635,19 @@
         <v>27</v>
       </c>
       <c r="GB9" s="3" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9961</v>
       </c>
       <c r="GC9" s="3" t="n">
         <v>0.1478</v>
       </c>
       <c r="GD9" s="3" t="n">
-        <v>0.0508</v>
+        <v>0.0509</v>
       </c>
       <c r="GE9" s="3" t="n">
         <v>0.003</v>
       </c>
       <c r="GF9" s="3" t="n">
-        <v>0.0399</v>
+        <v>0.04</v>
       </c>
       <c r="GG9" s="3" t="n">
         <v>0.0924</v>
@@ -8685,16 +8685,16 @@
         </is>
       </c>
       <c r="GR9" s="3" t="n">
-        <v>7.79</v>
+        <v>7.78</v>
       </c>
       <c r="GS9" s="3" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="GT9" s="3" t="n">
-        <v>12.1</v>
+        <v>12.12</v>
       </c>
       <c r="GU9" s="3" t="n">
-        <v>19.42</v>
+        <v>19.49</v>
       </c>
       <c r="GV9" s="3" t="n">
         <v>4.73</v>
@@ -8711,28 +8711,28 @@
         <v>78.09999999999999</v>
       </c>
       <c r="GZ9" s="3" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="HA9" s="3" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="HB9" s="3" t="n">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
       <c r="HC9" s="3" t="n">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
       <c r="HD9" s="3" t="n">
-        <v>53.5</v>
+        <v>53.8</v>
       </c>
       <c r="HE9" s="3" t="n">
-        <v>53.5</v>
+        <v>53.8</v>
       </c>
       <c r="HF9" s="3" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="HG9" s="3" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="HH9" s="3" t="n">
         <v>42.4</v>
@@ -8741,52 +8741,52 @@
         <v>42.4</v>
       </c>
       <c r="HJ9" s="3" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="HK9" s="3" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="HL9" s="3" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="HM9" s="3" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="HN9" s="3" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="HO9" s="3" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="HP9" s="3" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="HQ9" s="3" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="HR9" s="3" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="HS9" s="3" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="HT9" s="3" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="HU9" s="3" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="HV9" s="3" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="HW9" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="HX9" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="HY9" s="3" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="HZ9" s="3" t="n">
         <v>8</v>
@@ -8890,22 +8890,22 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>KC @ DET</t>
+          <t>MIN @ CLE</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -8915,143 +8915,143 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>7.64</v>
+        <v>7.77</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>7.64</v>
+        <v>7.77</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>4.91</v>
+        <v>6.25</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>8.16</v>
+        <v>6.41</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>7.43</v>
+        <v>6.26</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.27</v>
+        <v>7.29</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>7.4</v>
+        <v>6.26</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.022</v>
+        <v>0.858</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>7.7</v>
+        <v>10.4</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>7|0|23|16|2</t>
+          <t>3|6|22|7|12</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>7|0|23|16|2|9|3|2|15|0</t>
+          <t>3|6|22|7|12|3|14|4|19|14</t>
         </is>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>7|0|23|16|2|9|3|2|15|0|10|0|33|19|5</t>
+          <t>3|6|22|7|12|3|14|4|19|14|12|10|21|3|0</t>
         </is>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>80.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Z10" s="5" t="n">
-        <v>72.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="AA10" s="5" t="n">
-        <v>71.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="AB10" s="5" t="n">
-        <v>65.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="AD10" s="6" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="AE10" s="7" t="n">
-        <v>53.1</v>
+        <v>70.2</v>
+      </c>
+      <c r="AD10" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AE10" s="6" t="n">
+        <v>54.8</v>
       </c>
       <c r="AF10" s="7" t="n">
-        <v>48.9</v>
+        <v>54.3</v>
       </c>
       <c r="AG10" s="7" t="n">
-        <v>48.4</v>
+        <v>50.1</v>
       </c>
       <c r="AH10" s="7" t="n">
-        <v>40.6</v>
+        <v>49.6</v>
       </c>
       <c r="AI10" s="7" t="n">
-        <v>40.1</v>
+        <v>42.3</v>
       </c>
       <c r="AJ10" s="8" t="n">
-        <v>34.9</v>
+        <v>35.7</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>33.9</v>
+        <v>34.7</v>
       </c>
       <c r="AL10" s="8" t="n">
-        <v>29.4</v>
+        <v>30.7</v>
       </c>
       <c r="AM10" s="8" t="n">
-        <v>29.4</v>
+        <v>30.7</v>
       </c>
       <c r="AN10" s="8" t="n">
-        <v>29.4</v>
+        <v>26.6</v>
       </c>
       <c r="AO10" s="8" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="AP10" s="8" t="n">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="AQ10" s="8" t="n">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="AR10" s="8" t="n">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="AS10" s="8" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="AT10" s="8" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="AU10" s="8" t="n">
-        <v>20.3</v>
+        <v>17.2</v>
       </c>
       <c r="AV10" s="8" t="n">
-        <v>20.3</v>
+        <v>16.3</v>
       </c>
       <c r="AW10" s="8" t="n">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="AX10" s="8" t="n">
-        <v>17.1</v>
+        <v>13.5</v>
       </c>
       <c r="AY10" s="8" t="n">
-        <v>16.1</v>
+        <v>13.5</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>210.08</v>
+        <v>210.62</v>
       </c>
       <c r="BA10" s="4" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="BB10" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.5 | 64.6% | Edge +3.1</t>
+          <t>MORE 5.0 | 65.5% | Edge +2.8</t>
         </is>
       </c>
       <c r="BC10" s="4" t="inlineStr">
@@ -9069,16 +9069,16 @@
         </is>
       </c>
       <c r="BD10" s="3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE10" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="BF10" s="3" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="BG10" s="3" t="n">
-        <v>29.2</v>
+        <v>31</v>
       </c>
       <c r="BH10" s="4" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BJ10" s="4" t="inlineStr">
         <is>
@@ -9095,24 +9095,24 @@
       </c>
       <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM10" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN10" s="4" t="inlineStr">
         <is>
-          <t>4-5-4-4-4-5-4</t>
+          <t>3-3-3-3-3-3-3</t>
         </is>
       </c>
       <c r="BO10" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="BP10" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ10" s="3" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="BR10" s="4" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="BU10" s="4" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="BV10" s="4" t="inlineStr">
@@ -9136,51 +9136,51 @@
         </is>
       </c>
       <c r="BW10" s="3" t="n">
-        <v>1.93</v>
+        <v>3.85</v>
       </c>
       <c r="BX10" s="3" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="BY10" s="3" t="n">
-        <v>0.2097</v>
+        <v>0.2018</v>
       </c>
       <c r="BZ10" s="3" t="n">
-        <v>0.0323</v>
+        <v>0.0351</v>
       </c>
       <c r="CA10" s="3" t="n">
-        <v>0.129</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="CB10" s="3" t="n">
-        <v>4.93</v>
+        <v>4.77</v>
       </c>
       <c r="CC10" s="3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="CD10" s="3" t="n">
-        <v>0.2316</v>
+        <v>0.2253</v>
       </c>
       <c r="CE10" s="3" t="n">
-        <v>0.0352</v>
+        <v>0.0314</v>
       </c>
       <c r="CF10" s="4" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="CG10" s="3" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="CH10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="CI10" s="3" t="n">
-        <v>78.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="CJ10" s="3" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CK10" s="3" t="n">
-        <v>88</v>
+        <v>327</v>
       </c>
       <c r="CL10" s="3" t="n">
         <v>0</v>
@@ -9191,69 +9191,69 @@
         </is>
       </c>
       <c r="CN10" s="3" t="n">
-        <v>424</v>
+        <v>359</v>
       </c>
       <c r="CO10" s="3" t="n">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="CP10" s="3" t="n">
-        <v>0.285</v>
+        <v>0.287</v>
       </c>
       <c r="CQ10" s="3" t="n">
-        <v>0.375</v>
+        <v>0.351</v>
       </c>
       <c r="CR10" s="3" t="n">
-        <v>0.471</v>
+        <v>0.454</v>
       </c>
       <c r="CS10" s="3" t="n">
-        <v>0.846</v>
+        <v>0.805</v>
       </c>
       <c r="CT10" s="3" t="n">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="CU10" s="3" t="n">
-        <v>0.908</v>
+        <v>0.751</v>
       </c>
       <c r="CV10" s="3" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="CW10" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CX10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="CY10" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CZ10" s="3" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="DA10" s="3" t="n">
         <v>50</v>
       </c>
       <c r="DB10" s="3" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="DC10" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DD10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DE10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Chicago Cubs: 7 FS|2026-07-21 @ Chicago Cubs: 0 FS|2026-07-20 @ Chicago Cubs: 23 FS|2026-07-19 @ Los Angeles Angels: 16 FS|2026-07-18 @ Los Angeles Angels: 2 FS</t>
+          <t>2026-07-22 vs Minnesota Twins: 3 FS|2026-07-21 vs Minnesota Twins: 6 FS|2026-07-20 vs Minnesota Twins: 22 FS|2026-07-19 vs Pittsburgh Pirates: 7 FS|2026-07-18 vs Pittsburgh Pirates: 12 FS</t>
         </is>
       </c>
       <c r="DF10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Chicago Cubs: 7 FS|2026-07-21 @ Chicago Cubs: 0 FS|2026-07-20 @ Chicago Cubs: 23 FS|2026-07-19 @ Los Angeles Angels: 16 FS|2026-07-18 @ Los Angeles Angels: 2 FS|2026-07-17 @ Los Angeles Angels: 9 FS|2026-07-12 vs Philadelphia Phillies: 3 FS|2026-07-11 vs Philadelphia Phillies: 2 FS|2026-07-10 vs Philadelphia Phillies: 15 FS|2026-07-09 vs Athletics: 0 FS</t>
+          <t>2026-07-22 vs Minnesota Twins: 3 FS|2026-07-21 vs Minnesota Twins: 6 FS|2026-07-20 vs Minnesota Twins: 22 FS|2026-07-19 vs Pittsburgh Pirates: 7 FS|2026-07-18 vs Pittsburgh Pirates: 12 FS|2026-07-18 vs Pittsburgh Pirates: 3 FS|2026-07-12 @ Miami Marlins: 14 FS|2026-07-11 @ Miami Marlins: 4 FS|2026-07-10 @ Miami Marlins: 19 FS|2026-07-09 @ Minnesota Twins: 14 FS</t>
         </is>
       </c>
       <c r="DG10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Chicago Cubs: 7 FS|2026-07-21 @ Chicago Cubs: 0 FS|2026-07-20 @ Chicago Cubs: 23 FS|2026-07-19 @ Los Angeles Angels: 16 FS|2026-07-18 @ Los Angeles Angels: 2 FS|2026-07-17 @ Los Angeles Angels: 9 FS|2026-07-12 vs Philadelphia Phillies: 3 FS|2026-07-11 vs Philadelphia Phillies: 2 FS|2026-07-10 vs Philadelphia Phillies: 15 FS|2026-07-09 vs Athletics: 0 FS|2026-07-08 vs Athletics: 10 FS|2026-07-07 vs Athletics: 0 FS|2026-07-05 @ Texas Rangers: 33 FS|2026-07-04 @ Texas Rangers: 19 FS|2026-07-02 @ Texas Rangers: 5 FS</t>
+          <t>2026-07-22 vs Minnesota Twins: 3 FS|2026-07-21 vs Minnesota Twins: 6 FS|2026-07-20 vs Minnesota Twins: 22 FS|2026-07-19 vs Pittsburgh Pirates: 7 FS|2026-07-18 vs Pittsburgh Pirates: 12 FS|2026-07-18 vs Pittsburgh Pirates: 3 FS|2026-07-12 @ Miami Marlins: 14 FS|2026-07-11 @ Miami Marlins: 4 FS|2026-07-10 @ Miami Marlins: 19 FS|2026-07-09 @ Minnesota Twins: 14 FS|2026-07-08 @ Minnesota Twins: 12 FS|2026-07-07 @ Minnesota Twins: 10 FS|2026-07-05 vs Chicago White Sox: 21 FS|2026-07-04 vs Chicago White Sox: 3 FS|2026-07-03 vs Chicago White Sox: 0 FS</t>
         </is>
       </c>
       <c r="DH10" s="3" t="n">
@@ -9263,10 +9263,10 @@
         <v>30</v>
       </c>
       <c r="DJ10" s="3" t="n">
-        <v>8.43</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DK10" s="3" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="DL10" s="4" t="inlineStr">
         <is>
@@ -9274,54 +9274,54 @@
         </is>
       </c>
       <c r="DM10" s="3" t="n">
-        <v>8.57</v>
+        <v>9.57</v>
       </c>
       <c r="DN10" s="3" t="n">
-        <v>9.93</v>
+        <v>10.71</v>
       </c>
       <c r="DO10" s="3" t="n">
-        <v>0.292</v>
+        <v>0.368</v>
       </c>
       <c r="DP10" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="DQ10" s="3" t="n">
-        <v>8.43</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DR10" s="3" t="n">
-        <v>2.439</v>
+        <v>2.419</v>
       </c>
       <c r="DS10" s="3" t="n">
-        <v>0.2456</v>
+        <v>0.3387</v>
       </c>
       <c r="DT10" s="3" t="n">
-        <v>0.1404</v>
+        <v>0.129</v>
       </c>
       <c r="DU10" s="3" t="n">
-        <v>0.0702</v>
+        <v>0.0645</v>
       </c>
       <c r="DV10" s="3" t="n">
-        <v>0.1404</v>
+        <v>0.0806</v>
       </c>
       <c r="DW10" s="3" t="n">
-        <v>0</v>
+        <v>0.0161</v>
       </c>
       <c r="DX10" s="3" t="n">
-        <v>9.06</v>
+        <v>8.98</v>
       </c>
       <c r="DY10" s="3" t="n">
-        <v>9.289999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="DZ10" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="EA10" s="3" t="n">
-        <v>8.970000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="EB10" s="3" t="n">
-        <v>8.58</v>
+        <v>7.97</v>
       </c>
       <c r="EC10" s="3" t="n">
         <v>28</v>
@@ -9339,25 +9339,25 @@
         <v>20</v>
       </c>
       <c r="EH10" s="3" t="n">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="EI10" s="3" t="n">
-        <v>84.7</v>
+        <v>84.48</v>
       </c>
       <c r="EJ10" s="3" t="n">
-        <v>30.74</v>
+        <v>29.58</v>
       </c>
       <c r="EK10" s="3" t="n">
-        <v>1.95</v>
+        <v>0.47</v>
       </c>
       <c r="EL10" s="3" t="n">
-        <v>33.85</v>
+        <v>28.17</v>
       </c>
       <c r="EM10" s="3" t="n">
-        <v>0.43</v>
+        <v>0.385</v>
       </c>
       <c r="EN10" s="3" t="n">
-        <v>0.9902</v>
+        <v>0.9388</v>
       </c>
       <c r="EO10" s="3" t="n">
         <v>1</v>
@@ -9369,10 +9369,10 @@
         <v>1</v>
       </c>
       <c r="ER10" s="3" t="n">
-        <v>1.0123</v>
+        <v>1.0312</v>
       </c>
       <c r="ES10" s="3" t="n">
-        <v>671</v>
+        <v>305</v>
       </c>
       <c r="ET10" s="4" t="inlineStr">
         <is>
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="EU10" s="3" t="n">
-        <v>0.9385</v>
+        <v>1.0235</v>
       </c>
       <c r="EV10" s="3" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="EW10" s="4" t="inlineStr">
         <is>
@@ -9391,52 +9391,52 @@
         </is>
       </c>
       <c r="EX10" s="3" t="n">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="EY10" s="3" t="n">
-        <v>84.7</v>
+        <v>84.48</v>
       </c>
       <c r="EZ10" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FA10" s="3" t="n">
-        <v>18.6</v>
+        <v>15.96</v>
       </c>
       <c r="FB10" s="3" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="FC10" s="3" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="FD10" s="3" t="n">
-        <v>63.8</v>
+        <v>62.4</v>
       </c>
       <c r="FE10" s="3" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="FF10" s="3" t="n">
-        <v>1.0095</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="FG10" s="3" t="n">
-        <v>1.0138</v>
+        <v>1.002</v>
       </c>
       <c r="FH10" s="3" t="n">
-        <v>1.0951</v>
+        <v>0.9866</v>
       </c>
       <c r="FI10" s="3" t="n">
-        <v>1.1889</v>
+        <v>1.0041</v>
       </c>
       <c r="FJ10" s="3" t="n">
-        <v>0.9624</v>
+        <v>0.9926</v>
       </c>
       <c r="FK10" s="3" t="n">
-        <v>1.0064</v>
+        <v>1.0163</v>
       </c>
       <c r="FL10" s="3" t="n">
-        <v>8.970000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="FM10" s="3" t="n">
-        <v>0.53</v>
+        <v>1.36</v>
       </c>
       <c r="FN10" s="4" t="inlineStr">
         <is>
@@ -9481,52 +9481,52 @@
         <v>27</v>
       </c>
       <c r="FZ10" s="3" t="n">
-        <v>0.8861</v>
+        <v>1.0714</v>
       </c>
       <c r="GA10" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GB10" s="3" t="n">
-        <v>0.9702</v>
+        <v>0.9983</v>
       </c>
       <c r="GC10" s="3" t="n">
-        <v>0.1289</v>
+        <v>0.1481</v>
       </c>
       <c r="GD10" s="3" t="n">
         <v>0.0469</v>
       </c>
       <c r="GE10" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.0028</v>
       </c>
       <c r="GF10" s="3" t="n">
-        <v>0.0382</v>
+        <v>0.0358</v>
       </c>
       <c r="GG10" s="3" t="n">
-        <v>0.134</v>
+        <v>0.0926</v>
       </c>
       <c r="GH10" s="3" t="n">
-        <v>0.0101</v>
+        <v>0.0078</v>
       </c>
       <c r="GI10" s="3" t="n">
-        <v>0.2241</v>
+        <v>0.1782</v>
       </c>
       <c r="GJ10" s="3" t="n">
-        <v>0.3445</v>
+        <v>0.4775</v>
       </c>
       <c r="GK10" s="3" t="n">
-        <v>0.4035</v>
+        <v>0.2163</v>
       </c>
       <c r="GL10" s="3" t="n">
-        <v>0.2521</v>
+        <v>0.3063</v>
       </c>
       <c r="GM10" s="3" t="n">
-        <v>0.1167</v>
+        <v>0.109</v>
       </c>
       <c r="GN10" s="3" t="n">
-        <v>0.1481</v>
+        <v>0.1459</v>
       </c>
       <c r="GO10" s="3" t="n">
-        <v>0.008</v>
+        <v>0.0133</v>
       </c>
       <c r="GP10" s="3" t="n">
         <v>1</v>
@@ -9537,19 +9537,19 @@
         </is>
       </c>
       <c r="GR10" s="3" t="n">
-        <v>7.4</v>
+        <v>6.26</v>
       </c>
       <c r="GS10" s="3" t="n">
-        <v>1.85</v>
+        <v>2.82</v>
       </c>
       <c r="GT10" s="3" t="n">
-        <v>11.04</v>
+        <v>10.54</v>
       </c>
       <c r="GU10" s="3" t="n">
-        <v>18.19</v>
+        <v>16.55</v>
       </c>
       <c r="GV10" s="3" t="n">
-        <v>4.25</v>
+        <v>4.57</v>
       </c>
       <c r="GW10" s="3" t="n">
         <v>0</v>
@@ -9560,88 +9560,88 @@
         </is>
       </c>
       <c r="GY10" s="3" t="n">
-        <v>72.7</v>
+        <v>83.2</v>
       </c>
       <c r="GZ10" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="HA10" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="HB10" s="3" t="n">
-        <v>58.6</v>
+        <v>64.2</v>
       </c>
       <c r="HC10" s="3" t="n">
-        <v>58.6</v>
+        <v>64.2</v>
       </c>
       <c r="HD10" s="3" t="n">
-        <v>48.6</v>
+        <v>60.5</v>
       </c>
       <c r="HE10" s="3" t="n">
-        <v>48.6</v>
+        <v>50.3</v>
       </c>
       <c r="HF10" s="3" t="n">
-        <v>44.9</v>
+        <v>50.3</v>
       </c>
       <c r="HG10" s="3" t="n">
-        <v>44.9</v>
+        <v>46.6</v>
       </c>
       <c r="HH10" s="3" t="n">
-        <v>37.6</v>
+        <v>46.6</v>
       </c>
       <c r="HI10" s="3" t="n">
-        <v>37.6</v>
+        <v>39.8</v>
       </c>
       <c r="HJ10" s="3" t="n">
-        <v>33.9</v>
+        <v>34.7</v>
       </c>
       <c r="HK10" s="3" t="n">
-        <v>33.9</v>
+        <v>34.7</v>
       </c>
       <c r="HL10" s="3" t="n">
-        <v>29.4</v>
+        <v>30.7</v>
       </c>
       <c r="HM10" s="3" t="n">
-        <v>29.4</v>
+        <v>30.7</v>
       </c>
       <c r="HN10" s="3" t="n">
-        <v>29.4</v>
+        <v>26.6</v>
       </c>
       <c r="HO10" s="3" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="HP10" s="3" t="n">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="HQ10" s="3" t="n">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="HR10" s="3" t="n">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="HS10" s="3" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="HT10" s="3" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="HU10" s="3" t="n">
-        <v>20.3</v>
+        <v>17.2</v>
       </c>
       <c r="HV10" s="3" t="n">
-        <v>20.3</v>
+        <v>16.3</v>
       </c>
       <c r="HW10" s="3" t="n">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="HX10" s="3" t="n">
-        <v>17.1</v>
+        <v>13.5</v>
       </c>
       <c r="HY10" s="3" t="n">
-        <v>16.1</v>
+        <v>13.5</v>
       </c>
       <c r="HZ10" s="3" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="IA10" s="3" t="n">
         <v>8</v>
@@ -9742,22 +9742,22 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CLE</t>
+          <t>KC @ DET</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -9767,143 +9767,143 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>7.72</v>
+        <v>7.64</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>7.72</v>
+        <v>7.64</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>5.38</v>
+        <v>4.91</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>6.41</v>
+        <v>8.16</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>6.26</v>
+        <v>7.43</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.26</v>
+        <v>7.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.859</v>
+        <v>1.022</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>10.4</v>
+        <v>7.7</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>3|6|22|7|12</t>
+          <t>7|0|23|16|2</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>3|6|22|7|12|3|14|4|19|14</t>
+          <t>7|0|23|16|2|9|3|2|15|0</t>
         </is>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>3|6|22|7|12|3|14|4|19|14|12|10|21|3|0</t>
+          <t>7|0|23|16|2|9|3|2|15|0|10|0|33|19|5</t>
         </is>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>90.2</v>
+        <v>80.7</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>82.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AA11" s="5" t="n">
-        <v>82.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>70.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AE11" s="6" t="n">
-        <v>54</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AD11" s="6" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AE11" s="7" t="n">
+        <v>53</v>
       </c>
       <c r="AF11" s="7" t="n">
-        <v>53.5</v>
+        <v>48.9</v>
       </c>
       <c r="AG11" s="7" t="n">
-        <v>49.3</v>
+        <v>48.4</v>
       </c>
       <c r="AH11" s="7" t="n">
-        <v>48.8</v>
+        <v>40.6</v>
       </c>
       <c r="AI11" s="7" t="n">
-        <v>41.6</v>
+        <v>40.1</v>
       </c>
       <c r="AJ11" s="8" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="AL11" s="8" t="n">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="AM11" s="8" t="n">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="AN11" s="8" t="n">
-        <v>26.3</v>
+        <v>29.3</v>
       </c>
       <c r="AO11" s="8" t="n">
-        <v>26.3</v>
+        <v>25.7</v>
       </c>
       <c r="AP11" s="8" t="n">
-        <v>24.4</v>
+        <v>25.7</v>
       </c>
       <c r="AQ11" s="8" t="n">
-        <v>21.9</v>
+        <v>23.7</v>
       </c>
       <c r="AR11" s="8" t="n">
-        <v>21.9</v>
+        <v>23.7</v>
       </c>
       <c r="AS11" s="8" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="AT11" s="8" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="AU11" s="8" t="n">
-        <v>17.1</v>
+        <v>20.3</v>
       </c>
       <c r="AV11" s="8" t="n">
-        <v>16.2</v>
+        <v>20.3</v>
       </c>
       <c r="AW11" s="8" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="AX11" s="8" t="n">
-        <v>13.2</v>
+        <v>17.2</v>
       </c>
       <c r="AY11" s="8" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="AZ11" s="3" t="n">
-        <v>209.69</v>
+        <v>210.08</v>
       </c>
       <c r="BA11" s="4" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="BB11" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 65.0% | Edge +2.7</t>
+          <t>MORE 4.5 | 64.6% | Edge +3.1</t>
         </is>
       </c>
       <c r="BC11" s="4" t="inlineStr">
@@ -9921,16 +9921,16 @@
         </is>
       </c>
       <c r="BD11" s="3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" s="3" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="BF11" s="3" t="n">
-        <v>2.72</v>
+        <v>3.14</v>
       </c>
       <c r="BG11" s="3" t="n">
-        <v>30</v>
+        <v>29.2</v>
       </c>
       <c r="BH11" s="4" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         </is>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ11" s="4" t="inlineStr">
         <is>
@@ -9947,24 +9947,24 @@
       </c>
       <c r="BK11" s="4" t="n"/>
       <c r="BL11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM11" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN11" s="4" t="inlineStr">
         <is>
-          <t>3-3-3-3-3-3-3</t>
+          <t>4-5-4-4-4-5-4</t>
         </is>
       </c>
       <c r="BO11" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="BP11" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ11" s="3" t="n">
-        <v>4.92</v>
+        <v>4.82</v>
       </c>
       <c r="BR11" s="4" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="BU11" s="4" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="BV11" s="4" t="inlineStr">
@@ -9988,51 +9988,51 @@
         </is>
       </c>
       <c r="BW11" s="3" t="n">
-        <v>3.85</v>
+        <v>1.93</v>
       </c>
       <c r="BX11" s="3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="BY11" s="3" t="n">
-        <v>0.2018</v>
+        <v>0.2097</v>
       </c>
       <c r="BZ11" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.0323</v>
       </c>
       <c r="CA11" s="3" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="CB11" s="3" t="n">
-        <v>4.77</v>
+        <v>4.93</v>
       </c>
       <c r="CC11" s="3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="CD11" s="3" t="n">
-        <v>0.2253</v>
+        <v>0.2316</v>
       </c>
       <c r="CE11" s="3" t="n">
-        <v>0.0314</v>
+        <v>0.0352</v>
       </c>
       <c r="CF11" s="4" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="CG11" s="3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="CH11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="CI11" s="3" t="n">
-        <v>74.2</v>
+        <v>78.5</v>
       </c>
       <c r="CJ11" s="3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="CK11" s="3" t="n">
-        <v>337</v>
+        <v>88</v>
       </c>
       <c r="CL11" s="3" t="n">
         <v>0</v>
@@ -10043,69 +10043,69 @@
         </is>
       </c>
       <c r="CN11" s="3" t="n">
-        <v>359</v>
+        <v>424</v>
       </c>
       <c r="CO11" s="3" t="n">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="CP11" s="3" t="n">
-        <v>0.287</v>
+        <v>0.285</v>
       </c>
       <c r="CQ11" s="3" t="n">
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="CR11" s="3" t="n">
-        <v>0.454</v>
+        <v>0.471</v>
       </c>
       <c r="CS11" s="3" t="n">
-        <v>0.805</v>
+        <v>0.846</v>
       </c>
       <c r="CT11" s="3" t="n">
-        <v>249</v>
+        <v>289</v>
       </c>
       <c r="CU11" s="3" t="n">
-        <v>0.751</v>
+        <v>0.908</v>
       </c>
       <c r="CV11" s="3" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="CW11" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CX11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="CY11" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CZ11" s="3" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="DA11" s="3" t="n">
         <v>50</v>
       </c>
       <c r="DB11" s="3" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="DC11" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DD11" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DE11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Minnesota Twins: 3 FS|2026-07-21 vs Minnesota Twins: 6 FS|2026-07-20 vs Minnesota Twins: 22 FS|2026-07-19 vs Pittsburgh Pirates: 7 FS|2026-07-18 vs Pittsburgh Pirates: 12 FS</t>
+          <t>2026-07-22 @ Chicago Cubs: 7 FS|2026-07-21 @ Chicago Cubs: 0 FS|2026-07-20 @ Chicago Cubs: 23 FS|2026-07-19 @ Los Angeles Angels: 16 FS|2026-07-18 @ Los Angeles Angels: 2 FS</t>
         </is>
       </c>
       <c r="DF11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Minnesota Twins: 3 FS|2026-07-21 vs Minnesota Twins: 6 FS|2026-07-20 vs Minnesota Twins: 22 FS|2026-07-19 vs Pittsburgh Pirates: 7 FS|2026-07-18 vs Pittsburgh Pirates: 12 FS|2026-07-18 vs Pittsburgh Pirates: 3 FS|2026-07-12 @ Miami Marlins: 14 FS|2026-07-11 @ Miami Marlins: 4 FS|2026-07-10 @ Miami Marlins: 19 FS|2026-07-09 @ Minnesota Twins: 14 FS</t>
+          <t>2026-07-22 @ Chicago Cubs: 7 FS|2026-07-21 @ Chicago Cubs: 0 FS|2026-07-20 @ Chicago Cubs: 23 FS|2026-07-19 @ Los Angeles Angels: 16 FS|2026-07-18 @ Los Angeles Angels: 2 FS|2026-07-17 @ Los Angeles Angels: 9 FS|2026-07-12 vs Philadelphia Phillies: 3 FS|2026-07-11 vs Philadelphia Phillies: 2 FS|2026-07-10 vs Philadelphia Phillies: 15 FS|2026-07-09 vs Athletics: 0 FS</t>
         </is>
       </c>
       <c r="DG11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Minnesota Twins: 3 FS|2026-07-21 vs Minnesota Twins: 6 FS|2026-07-20 vs Minnesota Twins: 22 FS|2026-07-19 vs Pittsburgh Pirates: 7 FS|2026-07-18 vs Pittsburgh Pirates: 12 FS|2026-07-18 vs Pittsburgh Pirates: 3 FS|2026-07-12 @ Miami Marlins: 14 FS|2026-07-11 @ Miami Marlins: 4 FS|2026-07-10 @ Miami Marlins: 19 FS|2026-07-09 @ Minnesota Twins: 14 FS|2026-07-08 @ Minnesota Twins: 12 FS|2026-07-07 @ Minnesota Twins: 10 FS|2026-07-05 vs Chicago White Sox: 21 FS|2026-07-04 vs Chicago White Sox: 3 FS|2026-07-03 vs Chicago White Sox: 0 FS</t>
+          <t>2026-07-22 @ Chicago Cubs: 7 FS|2026-07-21 @ Chicago Cubs: 0 FS|2026-07-20 @ Chicago Cubs: 23 FS|2026-07-19 @ Los Angeles Angels: 16 FS|2026-07-18 @ Los Angeles Angels: 2 FS|2026-07-17 @ Los Angeles Angels: 9 FS|2026-07-12 vs Philadelphia Phillies: 3 FS|2026-07-11 vs Philadelphia Phillies: 2 FS|2026-07-10 vs Philadelphia Phillies: 15 FS|2026-07-09 vs Athletics: 0 FS|2026-07-08 vs Athletics: 10 FS|2026-07-07 vs Athletics: 0 FS|2026-07-05 @ Texas Rangers: 33 FS|2026-07-04 @ Texas Rangers: 19 FS|2026-07-02 @ Texas Rangers: 5 FS</t>
         </is>
       </c>
       <c r="DH11" s="3" t="n">
@@ -10115,10 +10115,10 @@
         <v>30</v>
       </c>
       <c r="DJ11" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="DK11" s="3" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="DL11" s="4" t="inlineStr">
         <is>
@@ -10126,54 +10126,54 @@
         </is>
       </c>
       <c r="DM11" s="3" t="n">
-        <v>9.57</v>
+        <v>8.57</v>
       </c>
       <c r="DN11" s="3" t="n">
-        <v>10.71</v>
+        <v>9.93</v>
       </c>
       <c r="DO11" s="3" t="n">
-        <v>0.368</v>
+        <v>0.292</v>
       </c>
       <c r="DP11" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="DQ11" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="DR11" s="3" t="n">
-        <v>2.419</v>
+        <v>2.439</v>
       </c>
       <c r="DS11" s="3" t="n">
-        <v>0.3387</v>
+        <v>0.2456</v>
       </c>
       <c r="DT11" s="3" t="n">
-        <v>0.129</v>
+        <v>0.1404</v>
       </c>
       <c r="DU11" s="3" t="n">
-        <v>0.0645</v>
+        <v>0.0702</v>
       </c>
       <c r="DV11" s="3" t="n">
-        <v>0.0806</v>
+        <v>0.1404</v>
       </c>
       <c r="DW11" s="3" t="n">
-        <v>0.0161</v>
+        <v>0</v>
       </c>
       <c r="DX11" s="3" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="DY11" s="3" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="DZ11" s="3" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="EA11" s="3" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="DY11" s="3" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="DZ11" s="3" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="EA11" s="3" t="n">
-        <v>9.1</v>
-      </c>
       <c r="EB11" s="3" t="n">
-        <v>7.97</v>
+        <v>8.58</v>
       </c>
       <c r="EC11" s="3" t="n">
         <v>28</v>
@@ -10191,25 +10191,25 @@
         <v>20</v>
       </c>
       <c r="EH11" s="3" t="n">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="EI11" s="3" t="n">
-        <v>84.48</v>
+        <v>84.7</v>
       </c>
       <c r="EJ11" s="3" t="n">
-        <v>29.58</v>
+        <v>30.74</v>
       </c>
       <c r="EK11" s="3" t="n">
-        <v>0.47</v>
+        <v>1.95</v>
       </c>
       <c r="EL11" s="3" t="n">
-        <v>28.17</v>
+        <v>33.85</v>
       </c>
       <c r="EM11" s="3" t="n">
-        <v>0.385</v>
+        <v>0.43</v>
       </c>
       <c r="EN11" s="3" t="n">
-        <v>0.9388</v>
+        <v>0.9902</v>
       </c>
       <c r="EO11" s="3" t="n">
         <v>1</v>
@@ -10221,10 +10221,10 @@
         <v>1</v>
       </c>
       <c r="ER11" s="3" t="n">
-        <v>1.0312</v>
+        <v>1.0123</v>
       </c>
       <c r="ES11" s="3" t="n">
-        <v>305</v>
+        <v>671</v>
       </c>
       <c r="ET11" s="4" t="inlineStr">
         <is>
@@ -10232,10 +10232,10 @@
         </is>
       </c>
       <c r="EU11" s="3" t="n">
-        <v>1.0235</v>
+        <v>0.9385</v>
       </c>
       <c r="EV11" s="3" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="EW11" s="4" t="inlineStr">
         <is>
@@ -10243,52 +10243,52 @@
         </is>
       </c>
       <c r="EX11" s="3" t="n">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="EY11" s="3" t="n">
-        <v>84.48</v>
+        <v>84.7</v>
       </c>
       <c r="EZ11" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FA11" s="3" t="n">
-        <v>15.96</v>
+        <v>18.6</v>
       </c>
       <c r="FB11" s="3" t="n">
-        <v>32.26</v>
+        <v>28.47</v>
       </c>
       <c r="FC11" s="3" t="n">
-        <v>15</v>
+        <v>13.2</v>
       </c>
       <c r="FD11" s="3" t="n">
-        <v>62.4</v>
+        <v>63.8</v>
       </c>
       <c r="FE11" s="3" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="FF11" s="3" t="n">
-        <v>0.9775</v>
+        <v>1.0095</v>
       </c>
       <c r="FG11" s="3" t="n">
-        <v>1.002</v>
+        <v>1.0138</v>
       </c>
       <c r="FH11" s="3" t="n">
-        <v>0.9848</v>
+        <v>1.0951</v>
       </c>
       <c r="FI11" s="3" t="n">
-        <v>1.0041</v>
+        <v>1.1889</v>
       </c>
       <c r="FJ11" s="3" t="n">
-        <v>0.9908</v>
+        <v>0.9624</v>
       </c>
       <c r="FK11" s="3" t="n">
-        <v>1.0163</v>
+        <v>1.0064</v>
       </c>
       <c r="FL11" s="3" t="n">
-        <v>9.49</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="FM11" s="3" t="n">
-        <v>1.36</v>
+        <v>0.53</v>
       </c>
       <c r="FN11" s="4" t="inlineStr">
         <is>
@@ -10333,52 +10333,52 @@
         <v>27</v>
       </c>
       <c r="FZ11" s="3" t="n">
-        <v>1.0714</v>
+        <v>0.8861</v>
       </c>
       <c r="GA11" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GB11" s="3" t="n">
-        <v>0.9976</v>
+        <v>0.9702</v>
       </c>
       <c r="GC11" s="3" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="GD11" s="3" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="GE11" s="3" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="GF11" s="3" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="GG11" s="3" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="GH11" s="3" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="GI11" s="3" t="n">
+        <v>0.2241</v>
+      </c>
+      <c r="GJ11" s="3" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="GK11" s="3" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="GL11" s="3" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="GM11" s="3" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="GN11" s="3" t="n">
         <v>0.1481</v>
       </c>
-      <c r="GD11" s="3" t="n">
-        <v>0.0468</v>
-      </c>
-      <c r="GE11" s="3" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="GF11" s="3" t="n">
-        <v>0.0358</v>
-      </c>
-      <c r="GG11" s="3" t="n">
-        <v>0.0926</v>
-      </c>
-      <c r="GH11" s="3" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="GI11" s="3" t="n">
-        <v>0.1782</v>
-      </c>
-      <c r="GJ11" s="3" t="n">
-        <v>0.4775</v>
-      </c>
-      <c r="GK11" s="3" t="n">
-        <v>0.2163</v>
-      </c>
-      <c r="GL11" s="3" t="n">
-        <v>0.3063</v>
-      </c>
-      <c r="GM11" s="3" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="GN11" s="3" t="n">
-        <v>0.1459</v>
-      </c>
       <c r="GO11" s="3" t="n">
-        <v>0.0133</v>
+        <v>0.008</v>
       </c>
       <c r="GP11" s="3" t="n">
         <v>1</v>
@@ -10389,19 +10389,19 @@
         </is>
       </c>
       <c r="GR11" s="3" t="n">
-        <v>6.26</v>
+        <v>7.4</v>
       </c>
       <c r="GS11" s="3" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="GT11" s="3" t="n">
-        <v>10.54</v>
+        <v>11.04</v>
       </c>
       <c r="GU11" s="3" t="n">
-        <v>16.55</v>
+        <v>18.19</v>
       </c>
       <c r="GV11" s="3" t="n">
-        <v>4.56</v>
+        <v>4.25</v>
       </c>
       <c r="GW11" s="3" t="n">
         <v>0</v>
@@ -10412,88 +10412,88 @@
         </is>
       </c>
       <c r="GY11" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="GZ11" s="3" t="n">
-        <v>74.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="HA11" s="3" t="n">
-        <v>74.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="HB11" s="3" t="n">
-        <v>63.8</v>
+        <v>58.6</v>
       </c>
       <c r="HC11" s="3" t="n">
-        <v>63.8</v>
+        <v>58.6</v>
       </c>
       <c r="HD11" s="3" t="n">
-        <v>60</v>
+        <v>48.5</v>
       </c>
       <c r="HE11" s="3" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="HF11" s="3" t="n">
-        <v>49.5</v>
+        <v>44.9</v>
       </c>
       <c r="HG11" s="3" t="n">
-        <v>45.8</v>
+        <v>44.9</v>
       </c>
       <c r="HH11" s="3" t="n">
-        <v>45.8</v>
+        <v>37.6</v>
       </c>
       <c r="HI11" s="3" t="n">
-        <v>39.1</v>
+        <v>37.6</v>
       </c>
       <c r="HJ11" s="3" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="HK11" s="3" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="HL11" s="3" t="n">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="HM11" s="3" t="n">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="HN11" s="3" t="n">
-        <v>26.3</v>
+        <v>29.3</v>
       </c>
       <c r="HO11" s="3" t="n">
-        <v>26.3</v>
+        <v>25.7</v>
       </c>
       <c r="HP11" s="3" t="n">
-        <v>24.4</v>
+        <v>25.7</v>
       </c>
       <c r="HQ11" s="3" t="n">
-        <v>21.9</v>
+        <v>23.7</v>
       </c>
       <c r="HR11" s="3" t="n">
-        <v>21.9</v>
+        <v>23.7</v>
       </c>
       <c r="HS11" s="3" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="HT11" s="3" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="HU11" s="3" t="n">
-        <v>17.1</v>
+        <v>20.3</v>
       </c>
       <c r="HV11" s="3" t="n">
-        <v>16.2</v>
+        <v>20.3</v>
       </c>
       <c r="HW11" s="3" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="HX11" s="3" t="n">
-        <v>13.2</v>
+        <v>17.2</v>
       </c>
       <c r="HY11" s="3" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="HZ11" s="3" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="IA11" s="3" t="n">
         <v>8</v>
@@ -10626,10 +10626,10 @@
         <v>8.630000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>8.19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>6.26</v>
@@ -10686,52 +10686,52 @@
         <v>71.8</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
       <c r="AD12" s="5" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="AF12" s="7" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="AG12" s="7" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="AH12" s="7" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="AI12" s="7" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="AJ12" s="7" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="AK12" s="8" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="AL12" s="8" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="AM12" s="8" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="AN12" s="8" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="AO12" s="8" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="AP12" s="8" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="AQ12" s="8" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="AR12" s="8" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="AS12" s="8" t="n">
         <v>23.6</v>
@@ -10740,22 +10740,22 @@
         <v>23.6</v>
       </c>
       <c r="AU12" s="8" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AV12" s="8" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AW12" s="8" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AX12" s="8" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AY12" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ12" s="3" t="n">
-        <v>209.09</v>
+        <v>209.28</v>
       </c>
       <c r="BA12" s="4" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="BB12" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 64.2% | Edge +3.2</t>
+          <t>MORE 5.0 | 64.3% | Edge +3.2</t>
         </is>
       </c>
       <c r="BC12" s="4" t="inlineStr">
@@ -10776,13 +10776,13 @@
         <v>5</v>
       </c>
       <c r="BE12" s="3" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="BF12" s="3" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="BG12" s="3" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="BH12" s="4" t="inlineStr">
         <is>
@@ -11236,13 +11236,13 @@
         <v>6.94</v>
       </c>
       <c r="GS12" s="3" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="GT12" s="3" t="n">
         <v>11.55</v>
       </c>
       <c r="GU12" s="3" t="n">
-        <v>18.6</v>
+        <v>18.59</v>
       </c>
       <c r="GV12" s="3" t="n">
         <v>4.15</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="GY12" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="GZ12" s="3" t="n">
         <v>73.2</v>
@@ -11268,52 +11268,52 @@
         <v>64.8</v>
       </c>
       <c r="HC12" s="3" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="HD12" s="3" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="HE12" s="3" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="HF12" s="3" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="HG12" s="3" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="HH12" s="3" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="HI12" s="3" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="HJ12" s="3" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="HK12" s="3" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="HL12" s="3" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="HM12" s="3" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="HN12" s="3" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="HO12" s="3" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="HP12" s="3" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="HQ12" s="3" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="HR12" s="3" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="HS12" s="3" t="n">
         <v>23.6</v>
@@ -11322,22 +11322,22 @@
         <v>23.6</v>
       </c>
       <c r="HU12" s="3" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="HV12" s="3" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="HW12" s="3" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="HX12" s="3" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="HY12" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="HZ12" s="3" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="IA12" s="3" t="n">
         <v>8</v>
@@ -11438,102 +11438,102 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>ARI @ STL</t>
+          <t>MIN @ CLE</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>9.91</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>7.68</v>
+        <v>7.91</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>7.68</v>
+        <v>7.91</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>5.43</v>
+        <v>5.34</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>6.44</v>
+        <v>7.3</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>6.28</v>
+        <v>6.84</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>7.5</v>
+        <v>7.74</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>6.28</v>
+        <v>6.84</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.838</v>
+        <v>0.884</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>9.93</v>
+        <v>10.27</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>0|3|14|11|5</t>
+          <t>14|2|5|18|9</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>0|3|14|11|5|5|14|5|5|18</t>
+          <t>14|2|5|18|9|7|7|21|3|2</t>
         </is>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>0|3|14|11|5|5|14|5|5|18|19|8|16|4|22</t>
+          <t>14|2|5|18|9|7|7|21|3|2|6|18|5|7|30</t>
         </is>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>88.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>81.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="AA13" s="5" t="n">
-        <v>81.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>69.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>68.3</v>
+        <v>63.9</v>
       </c>
       <c r="AD13" s="5" t="n">
-        <v>64.2</v>
+        <v>62.9</v>
       </c>
       <c r="AE13" s="6" t="n">
         <v>52.8</v>
@@ -11542,64 +11542,64 @@
         <v>52.3</v>
       </c>
       <c r="AG13" s="7" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="AH13" s="7" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="AI13" s="7" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="AJ13" s="8" t="n">
-        <v>34.4</v>
+        <v>36.2</v>
       </c>
       <c r="AK13" s="8" t="n">
-        <v>33.4</v>
+        <v>35.2</v>
       </c>
       <c r="AL13" s="8" t="n">
-        <v>30.6</v>
+        <v>31.8</v>
       </c>
       <c r="AM13" s="8" t="n">
-        <v>30.6</v>
+        <v>31.8</v>
       </c>
       <c r="AN13" s="8" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="AO13" s="8" t="n">
-        <v>25</v>
+        <v>28.9</v>
       </c>
       <c r="AP13" s="8" t="n">
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="AQ13" s="8" t="n">
-        <v>22.6</v>
+        <v>26.8</v>
       </c>
       <c r="AR13" s="8" t="n">
-        <v>22.6</v>
+        <v>24.6</v>
       </c>
       <c r="AS13" s="8" t="n">
-        <v>21.2</v>
+        <v>23.6</v>
       </c>
       <c r="AT13" s="8" t="n">
-        <v>17.4</v>
+        <v>23.6</v>
       </c>
       <c r="AU13" s="8" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="AV13" s="8" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="AW13" s="8" t="n">
-        <v>16.7</v>
+        <v>18.7</v>
       </c>
       <c r="AX13" s="8" t="n">
-        <v>13.4</v>
+        <v>18.7</v>
       </c>
       <c r="AY13" s="8" t="n">
-        <v>11.7</v>
+        <v>14.9</v>
       </c>
       <c r="AZ13" s="3" t="n">
-        <v>206.08</v>
+        <v>207.04</v>
       </c>
       <c r="BA13" s="4" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="BB13" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 64.2% | Edge +2.7</t>
+          <t>MORE 5.0 | 62.9% | Edge +2.9</t>
         </is>
       </c>
       <c r="BC13" s="4" t="inlineStr">
@@ -11620,13 +11620,13 @@
         <v>5</v>
       </c>
       <c r="BE13" s="3" t="n">
-        <v>64.2</v>
+        <v>62.9</v>
       </c>
       <c r="BF13" s="3" t="n">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="BG13" s="3" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="BH13" s="4" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         </is>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BJ13" s="4" t="inlineStr">
         <is>
@@ -11643,24 +11643,24 @@
       </c>
       <c r="BK13" s="4" t="n"/>
       <c r="BL13" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM13" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BN13" s="4" t="inlineStr">
         <is>
-          <t>3-4-4-3-4-4-3</t>
+          <t>3-2-2-2-2</t>
         </is>
       </c>
       <c r="BO13" s="3" t="n">
-        <v>57.1</v>
+        <v>80</v>
       </c>
       <c r="BP13" s="3" t="n">
-        <v>97</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BQ13" s="3" t="n">
-        <v>4.82</v>
+        <v>4.94</v>
       </c>
       <c r="BR13" s="4" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="BU13" s="4" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="BV13" s="4" t="inlineStr">
@@ -11684,124 +11684,124 @@
         </is>
       </c>
       <c r="BW13" s="3" t="n">
-        <v>4.58</v>
+        <v>4</v>
       </c>
       <c r="BX13" s="3" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="BY13" s="3" t="n">
-        <v>0.2323</v>
+        <v>0.2062</v>
       </c>
       <c r="BZ13" s="3" t="n">
-        <v>0.0315</v>
+        <v>0.0412</v>
       </c>
       <c r="CA13" s="3" t="n">
-        <v>0.0709</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="CB13" s="3" t="n">
-        <v>4.21</v>
+        <v>3.74</v>
       </c>
       <c r="CC13" s="3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="CD13" s="3" t="n">
-        <v>0.2264</v>
+        <v>0.2123</v>
       </c>
       <c r="CE13" s="3" t="n">
-        <v>0.0322</v>
+        <v>0.0304</v>
       </c>
       <c r="CF13" s="4" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="CG13" s="3" t="n">
         <v>0.99</v>
       </c>
       <c r="CH13" s="3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="CI13" s="3" t="n">
-        <v>83.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="CJ13" s="3" t="n">
-        <v>4.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CK13" s="3" t="n">
+        <v>327</v>
+      </c>
+      <c r="CL13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" s="4" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="CN13" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="CO13" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="CP13" s="3" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="CQ13" s="3" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CR13" s="3" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="CS13" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CT13" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="CU13" s="3" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="CV13" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="CW13" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="CL13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CM13" s="4" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="CN13" s="3" t="n">
-        <v>422</v>
-      </c>
-      <c r="CO13" s="3" t="n">
-        <v>381</v>
-      </c>
-      <c r="CP13" s="3" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="CQ13" s="3" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="CR13" s="3" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="CS13" s="3" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="CT13" s="3" t="n">
-        <v>312</v>
-      </c>
-      <c r="CU13" s="3" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="CV13" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="CW13" s="3" t="n">
-        <v>21</v>
-      </c>
       <c r="CX13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY13" s="3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CZ13" s="3" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="DA13" s="3" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="DB13" s="3" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="DC13" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DD13" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="DE13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS</t>
+          <t>2026-07-21 @ Cleveland Guardians: 14 FS|2026-07-19 @ Chicago Cubs: 2 FS|2026-07-18 @ Chicago Cubs: 5 FS|2026-07-17 @ Chicago Cubs: 18 FS|2026-07-12 vs Los Angeles Angels: 9 FS</t>
         </is>
       </c>
       <c r="DF13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS</t>
+          <t>2026-07-21 @ Cleveland Guardians: 14 FS|2026-07-19 @ Chicago Cubs: 2 FS|2026-07-18 @ Chicago Cubs: 5 FS|2026-07-17 @ Chicago Cubs: 18 FS|2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS</t>
         </is>
       </c>
       <c r="DG13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS|2026-07-05 @ Chicago Cubs: 22 FS</t>
+          <t>2026-07-21 @ Cleveland Guardians: 14 FS|2026-07-19 @ Chicago Cubs: 2 FS|2026-07-18 @ Chicago Cubs: 5 FS|2026-07-17 @ Chicago Cubs: 18 FS|2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS|2026-05-14 vs Miami Marlins: 6 FS|2026-05-12 vs Miami Marlins: 18 FS|2026-05-10 @ Cleveland Guardians: 5 FS|2026-05-08 @ Cleveland Guardians: 7 FS|2026-05-07 @ Washington Nationals: 30 FS</t>
         </is>
       </c>
       <c r="DH13" s="3" t="n">
@@ -11811,7 +11811,7 @@
         <v>30</v>
       </c>
       <c r="DJ13" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="DK13" s="3" t="n">
         <v>6.5</v>
@@ -11822,13 +11822,13 @@
         </is>
       </c>
       <c r="DM13" s="3" t="n">
-        <v>7.43</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DN13" s="3" t="n">
-        <v>9.07</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DO13" s="3" t="n">
-        <v>0.269</v>
+        <v>0.255</v>
       </c>
       <c r="DP13" s="4" t="inlineStr">
         <is>
@@ -11836,40 +11836,40 @@
         </is>
       </c>
       <c r="DQ13" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="DR13" s="3" t="n">
-        <v>2.19</v>
+        <v>2.214</v>
       </c>
       <c r="DS13" s="3" t="n">
-        <v>0.2414</v>
+        <v>0.2143</v>
       </c>
       <c r="DT13" s="3" t="n">
-        <v>0.0862</v>
+        <v>0.1429</v>
       </c>
       <c r="DU13" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="DV13" s="3" t="n">
-        <v>0.1034</v>
+        <v>0.1607</v>
       </c>
       <c r="DW13" s="3" t="n">
-        <v>0.0517</v>
+        <v>0</v>
       </c>
       <c r="DX13" s="3" t="n">
-        <v>10.96</v>
+        <v>9.44</v>
       </c>
       <c r="DY13" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="DZ13" s="3" t="n">
-        <v>9.92</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="EA13" s="3" t="n">
-        <v>8.91</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="EB13" s="3" t="n">
-        <v>9.27</v>
+        <v>8.59</v>
       </c>
       <c r="EC13" s="3" t="n">
         <v>28</v>
@@ -11887,25 +11887,25 @@
         <v>20</v>
       </c>
       <c r="EH13" s="3" t="n">
-        <v>252</v>
+        <v>27</v>
       </c>
       <c r="EI13" s="3" t="n">
-        <v>85.95999999999999</v>
+        <v>84.41</v>
       </c>
       <c r="EJ13" s="3" t="n">
-        <v>30.16</v>
+        <v>18.52</v>
       </c>
       <c r="EK13" s="3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="EL13" s="3" t="n">
-        <v>29.37</v>
+        <v>33.33</v>
       </c>
       <c r="EM13" s="3" t="n">
-        <v>0.445</v>
+        <v>0.369</v>
       </c>
       <c r="EN13" s="3" t="n">
-        <v>1.0188</v>
+        <v>0.8891</v>
       </c>
       <c r="EO13" s="3" t="n">
         <v>1</v>
@@ -11917,10 +11917,10 @@
         <v>1</v>
       </c>
       <c r="ER13" s="3" t="n">
-        <v>1.0379</v>
+        <v>1.1378</v>
       </c>
       <c r="ES13" s="3" t="n">
-        <v>538</v>
+        <v>71</v>
       </c>
       <c r="ET13" s="4" t="inlineStr">
         <is>
@@ -11928,63 +11928,63 @@
         </is>
       </c>
       <c r="EU13" s="3" t="n">
-        <v>0.9867</v>
+        <v>1</v>
       </c>
       <c r="EV13" s="3" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="EW13" s="4" t="inlineStr">
         <is>
-          <t>Statcast</t>
+          <t>Fallback</t>
         </is>
       </c>
       <c r="EX13" s="3" t="n">
-        <v>252</v>
+        <v>27</v>
       </c>
       <c r="EY13" s="3" t="n">
-        <v>85.95999999999999</v>
+        <v>84.41</v>
       </c>
       <c r="EZ13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FA13" s="3" t="n">
-        <v>12.16</v>
+        <v>14.56</v>
       </c>
       <c r="FB13" s="3" t="n">
-        <v>34.2</v>
+        <v>30.59</v>
       </c>
       <c r="FC13" s="3" t="n">
-        <v>22.6</v>
+        <v>33.3</v>
       </c>
       <c r="FD13" s="3" t="n">
-        <v>62.7</v>
+        <v>55.6</v>
       </c>
       <c r="FE13" s="3" t="n">
-        <v>14.7</v>
+        <v>11.1</v>
       </c>
       <c r="FF13" s="3" t="n">
-        <v>0.9979</v>
+        <v>0.9804</v>
       </c>
       <c r="FG13" s="3" t="n">
-        <v>1.0044</v>
+        <v>1.0013</v>
       </c>
       <c r="FH13" s="3" t="n">
-        <v>1.0141</v>
+        <v>0.985</v>
       </c>
       <c r="FI13" s="3" t="n">
-        <v>1.0089</v>
+        <v>1.0025</v>
       </c>
       <c r="FJ13" s="3" t="n">
-        <v>1.0274</v>
+        <v>0.9887</v>
       </c>
       <c r="FK13" s="3" t="n">
-        <v>1.0001</v>
+        <v>1.0025</v>
       </c>
       <c r="FL13" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="FM13" s="3" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="FN13" s="4" t="inlineStr">
         <is>
@@ -12029,52 +12029,52 @@
         <v>27</v>
       </c>
       <c r="FZ13" s="3" t="n">
-        <v>1.3</v>
+        <v>0.8625</v>
       </c>
       <c r="GA13" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GB13" s="3" t="n">
-        <v>0.9895</v>
+        <v>0.9829</v>
       </c>
       <c r="GC13" s="3" t="n">
-        <v>0.1519</v>
+        <v>0.1069</v>
       </c>
       <c r="GD13" s="3" t="n">
-        <v>0.0524</v>
+        <v>0.0448</v>
       </c>
       <c r="GE13" s="3" t="n">
-        <v>0.0027</v>
+        <v>0.0034</v>
       </c>
       <c r="GF13" s="3" t="n">
-        <v>0.042</v>
+        <v>0.0464</v>
       </c>
       <c r="GG13" s="3" t="n">
-        <v>0.0756</v>
+        <v>0.1056</v>
       </c>
       <c r="GH13" s="3" t="n">
-        <v>0.008</v>
+        <v>0.0086</v>
       </c>
       <c r="GI13" s="3" t="n">
-        <v>0.2213</v>
+        <v>0.1997</v>
       </c>
       <c r="GJ13" s="3" t="n">
-        <v>0.4853</v>
+        <v>0.5</v>
       </c>
       <c r="GK13" s="3" t="n">
-        <v>0.2059</v>
+        <v>0.3125</v>
       </c>
       <c r="GL13" s="3" t="n">
-        <v>0.3089</v>
+        <v>0.1875</v>
       </c>
       <c r="GM13" s="3" t="n">
-        <v>0.1297</v>
+        <v>0.1352</v>
       </c>
       <c r="GN13" s="3" t="n">
-        <v>0.1732</v>
+        <v>0.1421</v>
       </c>
       <c r="GO13" s="3" t="n">
-        <v>0.0254</v>
+        <v>0.0089</v>
       </c>
       <c r="GP13" s="3" t="n">
         <v>1</v>
@@ -12085,19 +12085,19 @@
         </is>
       </c>
       <c r="GR13" s="3" t="n">
-        <v>6.28</v>
+        <v>6.84</v>
       </c>
       <c r="GS13" s="3" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="GT13" s="3" t="n">
-        <v>11.3</v>
+        <v>11.53</v>
       </c>
       <c r="GU13" s="3" t="n">
-        <v>17.16</v>
+        <v>17.72</v>
       </c>
       <c r="GV13" s="3" t="n">
-        <v>4.21</v>
+        <v>4.63</v>
       </c>
       <c r="GW13" s="3" t="n">
         <v>0</v>
@@ -12108,22 +12108,22 @@
         </is>
       </c>
       <c r="GY13" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="GZ13" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="HA13" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="HB13" s="3" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="HC13" s="3" t="n">
-        <v>62.3</v>
+        <v>57.9</v>
       </c>
       <c r="HD13" s="3" t="n">
-        <v>59.2</v>
+        <v>57.9</v>
       </c>
       <c r="HE13" s="3" t="n">
         <v>48.3</v>
@@ -12132,64 +12132,64 @@
         <v>48.3</v>
       </c>
       <c r="HG13" s="3" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="HH13" s="3" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="HI13" s="3" t="n">
-        <v>37.8</v>
+        <v>38.3</v>
       </c>
       <c r="HJ13" s="3" t="n">
-        <v>33.4</v>
+        <v>35.2</v>
       </c>
       <c r="HK13" s="3" t="n">
-        <v>33.4</v>
+        <v>35.2</v>
       </c>
       <c r="HL13" s="3" t="n">
-        <v>30.6</v>
+        <v>31.8</v>
       </c>
       <c r="HM13" s="3" t="n">
-        <v>30.6</v>
+        <v>31.8</v>
       </c>
       <c r="HN13" s="3" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="HO13" s="3" t="n">
-        <v>25</v>
+        <v>28.9</v>
       </c>
       <c r="HP13" s="3" t="n">
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="HQ13" s="3" t="n">
-        <v>22.6</v>
+        <v>26.8</v>
       </c>
       <c r="HR13" s="3" t="n">
-        <v>22.6</v>
+        <v>24.6</v>
       </c>
       <c r="HS13" s="3" t="n">
-        <v>21.2</v>
+        <v>23.6</v>
       </c>
       <c r="HT13" s="3" t="n">
-        <v>17.4</v>
+        <v>23.6</v>
       </c>
       <c r="HU13" s="3" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="HV13" s="3" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="HW13" s="3" t="n">
-        <v>16.7</v>
+        <v>18.7</v>
       </c>
       <c r="HX13" s="3" t="n">
-        <v>13.4</v>
+        <v>18.7</v>
       </c>
       <c r="HY13" s="3" t="n">
-        <v>11.7</v>
+        <v>14.9</v>
       </c>
       <c r="HZ13" s="3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="IA13" s="3" t="n">
         <v>8</v>
@@ -12290,168 +12290,168 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CLE</t>
+          <t>ARI @ STL</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>5.31</v>
+        <v>5.43</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>7.3</v>
+        <v>6.44</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>6.84</v>
+        <v>6.28</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>7.7</v>
+        <v>7.49</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>6.84</v>
+        <v>6.28</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.889</v>
+        <v>0.838</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>10.27</v>
+        <v>9.93</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>14|2|5|18|9</t>
+          <t>0|3|14|11|5</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>14|2|5|18|9|7|7|21|3|2</t>
+          <t>0|3|14|11|5|5|14|5|5|18</t>
         </is>
       </c>
       <c r="X14" s="4" t="inlineStr">
         <is>
-          <t>14|2|5|18|9|7|7|21|3|2|6|18|5|7|30</t>
+          <t>0|3|14|11|5|5|14|5|5|18|19|8|16|4|22</t>
         </is>
       </c>
       <c r="Y14" s="5" t="n">
         <v>88.5</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>79</v>
+        <v>81.5</v>
       </c>
       <c r="AA14" s="5" t="n">
-        <v>78.5</v>
+        <v>81</v>
       </c>
       <c r="AB14" s="5" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>63.3</v>
+        <v>68.2</v>
       </c>
       <c r="AD14" s="5" t="n">
-        <v>62.3</v>
+        <v>64.2</v>
       </c>
       <c r="AE14" s="6" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="AF14" s="7" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="AG14" s="7" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="AH14" s="7" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="AI14" s="7" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="AJ14" s="8" t="n">
-        <v>35.8</v>
+        <v>34.4</v>
       </c>
       <c r="AK14" s="8" t="n">
-        <v>34.8</v>
+        <v>33.4</v>
       </c>
       <c r="AL14" s="8" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="AM14" s="8" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="AN14" s="8" t="n">
-        <v>28.1</v>
+        <v>26.9</v>
       </c>
       <c r="AO14" s="8" t="n">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="AP14" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ14" s="8" t="n">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="AR14" s="8" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
       <c r="AS14" s="8" t="n">
-        <v>22.9</v>
+        <v>21.2</v>
       </c>
       <c r="AT14" s="8" t="n">
-        <v>22.9</v>
+        <v>17.5</v>
       </c>
       <c r="AU14" s="8" t="n">
-        <v>19.1</v>
+        <v>17.5</v>
       </c>
       <c r="AV14" s="8" t="n">
-        <v>19.1</v>
+        <v>16.7</v>
       </c>
       <c r="AW14" s="8" t="n">
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
       <c r="AX14" s="8" t="n">
-        <v>18.3</v>
+        <v>13.4</v>
       </c>
       <c r="AY14" s="8" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="AZ14" s="3" t="n">
-        <v>205.43</v>
+        <v>205.96</v>
       </c>
       <c r="BA14" s="4" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="BB14" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 62.3% | Edge +2.8</t>
+          <t>MORE 5.0 | 64.2% | Edge +2.7</t>
         </is>
       </c>
       <c r="BC14" s="4" t="inlineStr">
@@ -12472,13 +12472,13 @@
         <v>5</v>
       </c>
       <c r="BE14" s="3" t="n">
-        <v>62.3</v>
+        <v>64.2</v>
       </c>
       <c r="BF14" s="3" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="BG14" s="3" t="n">
-        <v>24.6</v>
+        <v>28.4</v>
       </c>
       <c r="BH14" s="4" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ14" s="4" t="inlineStr">
         <is>
@@ -12495,24 +12495,24 @@
       </c>
       <c r="BK14" s="4" t="n"/>
       <c r="BL14" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BM14" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BN14" s="4" t="inlineStr">
         <is>
-          <t>3-2-2-2-2</t>
+          <t>3-4-4-3-4-4-3</t>
         </is>
       </c>
       <c r="BO14" s="3" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="BP14" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="BQ14" s="3" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="BR14" s="4" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="BU14" s="4" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="BV14" s="4" t="inlineStr">
@@ -12536,124 +12536,124 @@
         </is>
       </c>
       <c r="BW14" s="3" t="n">
-        <v>4</v>
+        <v>4.58</v>
       </c>
       <c r="BX14" s="3" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="BY14" s="3" t="n">
-        <v>0.2062</v>
+        <v>0.2323</v>
       </c>
       <c r="BZ14" s="3" t="n">
-        <v>0.0412</v>
+        <v>0.0315</v>
       </c>
       <c r="CA14" s="3" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="CB14" s="3" t="n">
-        <v>3.74</v>
+        <v>4.21</v>
       </c>
       <c r="CC14" s="3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CD14" s="3" t="n">
-        <v>0.2123</v>
+        <v>0.2264</v>
       </c>
       <c r="CE14" s="3" t="n">
-        <v>0.0304</v>
+        <v>0.0322</v>
       </c>
       <c r="CF14" s="4" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="CG14" s="3" t="n">
         <v>0.99</v>
       </c>
       <c r="CH14" s="3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="CI14" s="3" t="n">
-        <v>74.2</v>
+        <v>83.5</v>
       </c>
       <c r="CJ14" s="3" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="CK14" s="3" t="n">
-        <v>337</v>
+        <v>9</v>
       </c>
       <c r="CL14" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CM14" s="4" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CN14" s="3" t="n">
-        <v>172</v>
+        <v>422</v>
       </c>
       <c r="CO14" s="3" t="n">
-        <v>143</v>
+        <v>381</v>
       </c>
       <c r="CP14" s="3" t="n">
-        <v>0.287</v>
+        <v>0.289</v>
       </c>
       <c r="CQ14" s="3" t="n">
-        <v>0.398</v>
+        <v>0.351</v>
       </c>
       <c r="CR14" s="3" t="n">
-        <v>0.552</v>
+        <v>0.517</v>
       </c>
       <c r="CS14" s="3" t="n">
-        <v>0.95</v>
+        <v>0.868</v>
       </c>
       <c r="CT14" s="3" t="n">
-        <v>105</v>
+        <v>312</v>
       </c>
       <c r="CU14" s="3" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.842</v>
       </c>
       <c r="CV14" s="3" t="n">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="CW14" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="CX14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY14" s="3" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="CZ14" s="3" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="DA14" s="3" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="DB14" s="3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="DC14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DD14" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="DE14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21 @ Cleveland Guardians: 14 FS|2026-07-19 @ Chicago Cubs: 2 FS|2026-07-18 @ Chicago Cubs: 5 FS|2026-07-17 @ Chicago Cubs: 18 FS|2026-07-12 vs Los Angeles Angels: 9 FS</t>
+          <t>2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS</t>
         </is>
       </c>
       <c r="DF14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21 @ Cleveland Guardians: 14 FS|2026-07-19 @ Chicago Cubs: 2 FS|2026-07-18 @ Chicago Cubs: 5 FS|2026-07-17 @ Chicago Cubs: 18 FS|2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS</t>
+          <t>2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS</t>
         </is>
       </c>
       <c r="DG14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21 @ Cleveland Guardians: 14 FS|2026-07-19 @ Chicago Cubs: 2 FS|2026-07-18 @ Chicago Cubs: 5 FS|2026-07-17 @ Chicago Cubs: 18 FS|2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS|2026-05-14 vs Miami Marlins: 6 FS|2026-05-12 vs Miami Marlins: 18 FS|2026-05-10 @ Cleveland Guardians: 5 FS|2026-05-08 @ Cleveland Guardians: 7 FS|2026-05-07 @ Washington Nationals: 30 FS</t>
+          <t>2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS|2026-07-05 @ Chicago Cubs: 22 FS</t>
         </is>
       </c>
       <c r="DH14" s="3" t="n">
@@ -12663,7 +12663,7 @@
         <v>30</v>
       </c>
       <c r="DJ14" s="3" t="n">
-        <v>9.1</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DK14" s="3" t="n">
         <v>6.5</v>
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="DM14" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="DN14" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DO14" s="3" t="n">
-        <v>0.255</v>
+        <v>0.269</v>
       </c>
       <c r="DP14" s="4" t="inlineStr">
         <is>
@@ -12688,40 +12688,40 @@
         </is>
       </c>
       <c r="DQ14" s="3" t="n">
-        <v>9.1</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DR14" s="3" t="n">
-        <v>2.214</v>
+        <v>2.19</v>
       </c>
       <c r="DS14" s="3" t="n">
-        <v>0.2143</v>
+        <v>0.2414</v>
       </c>
       <c r="DT14" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.0862</v>
       </c>
       <c r="DU14" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0345</v>
       </c>
       <c r="DV14" s="3" t="n">
-        <v>0.1607</v>
+        <v>0.1034</v>
       </c>
       <c r="DW14" s="3" t="n">
-        <v>0</v>
+        <v>0.0517</v>
       </c>
       <c r="DX14" s="3" t="n">
-        <v>9.43</v>
+        <v>10.96</v>
       </c>
       <c r="DY14" s="3" t="n">
-        <v>9.91</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ14" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="EA14" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="EB14" s="3" t="n">
-        <v>8.58</v>
+        <v>9.27</v>
       </c>
       <c r="EC14" s="3" t="n">
         <v>28</v>
@@ -12739,25 +12739,25 @@
         <v>20</v>
       </c>
       <c r="EH14" s="3" t="n">
-        <v>27</v>
+        <v>252</v>
       </c>
       <c r="EI14" s="3" t="n">
-        <v>84.41</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="EJ14" s="3" t="n">
-        <v>18.52</v>
+        <v>30.16</v>
       </c>
       <c r="EK14" s="3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="EL14" s="3" t="n">
-        <v>33.33</v>
+        <v>29.37</v>
       </c>
       <c r="EM14" s="3" t="n">
-        <v>0.369</v>
+        <v>0.445</v>
       </c>
       <c r="EN14" s="3" t="n">
-        <v>0.8891</v>
+        <v>1.0188</v>
       </c>
       <c r="EO14" s="3" t="n">
         <v>1</v>
@@ -12769,10 +12769,10 @@
         <v>1</v>
       </c>
       <c r="ER14" s="3" t="n">
-        <v>1.1378</v>
+        <v>1.0379</v>
       </c>
       <c r="ES14" s="3" t="n">
-        <v>71</v>
+        <v>538</v>
       </c>
       <c r="ET14" s="4" t="inlineStr">
         <is>
@@ -12780,63 +12780,63 @@
         </is>
       </c>
       <c r="EU14" s="3" t="n">
-        <v>1</v>
+        <v>0.9867</v>
       </c>
       <c r="EV14" s="3" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="EW14" s="4" t="inlineStr">
         <is>
-          <t>Fallback</t>
+          <t>Statcast</t>
         </is>
       </c>
       <c r="EX14" s="3" t="n">
-        <v>27</v>
+        <v>252</v>
       </c>
       <c r="EY14" s="3" t="n">
-        <v>84.41</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="EZ14" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FA14" s="3" t="n">
-        <v>14.56</v>
+        <v>12.16</v>
       </c>
       <c r="FB14" s="3" t="n">
-        <v>30.59</v>
+        <v>34.2</v>
       </c>
       <c r="FC14" s="3" t="n">
-        <v>33.3</v>
+        <v>22.6</v>
       </c>
       <c r="FD14" s="3" t="n">
-        <v>55.6</v>
+        <v>62.7</v>
       </c>
       <c r="FE14" s="3" t="n">
-        <v>11.1</v>
+        <v>14.7</v>
       </c>
       <c r="FF14" s="3" t="n">
-        <v>0.9787</v>
+        <v>0.9979</v>
       </c>
       <c r="FG14" s="3" t="n">
-        <v>1.0013</v>
+        <v>1.0044</v>
       </c>
       <c r="FH14" s="3" t="n">
-        <v>0.9833</v>
+        <v>1.0141</v>
       </c>
       <c r="FI14" s="3" t="n">
-        <v>1.0025</v>
+        <v>1.0089</v>
       </c>
       <c r="FJ14" s="3" t="n">
-        <v>0.987</v>
+        <v>1.0274</v>
       </c>
       <c r="FK14" s="3" t="n">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="FL14" s="3" t="n">
-        <v>9.31</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="FM14" s="3" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="FN14" s="4" t="inlineStr">
         <is>
@@ -12881,52 +12881,52 @@
         <v>27</v>
       </c>
       <c r="FZ14" s="3" t="n">
-        <v>0.8625</v>
+        <v>1.3</v>
       </c>
       <c r="GA14" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GB14" s="3" t="n">
-        <v>0.9811</v>
+        <v>0.9895</v>
       </c>
       <c r="GC14" s="3" t="n">
-        <v>0.1069</v>
+        <v>0.1519</v>
       </c>
       <c r="GD14" s="3" t="n">
-        <v>0.0447</v>
+        <v>0.0524</v>
       </c>
       <c r="GE14" s="3" t="n">
-        <v>0.0034</v>
+        <v>0.0027</v>
       </c>
       <c r="GF14" s="3" t="n">
-        <v>0.0464</v>
+        <v>0.042</v>
       </c>
       <c r="GG14" s="3" t="n">
-        <v>0.1056</v>
+        <v>0.0756</v>
       </c>
       <c r="GH14" s="3" t="n">
-        <v>0.0086</v>
+        <v>0.008</v>
       </c>
       <c r="GI14" s="3" t="n">
-        <v>0.1997</v>
+        <v>0.2213</v>
       </c>
       <c r="GJ14" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4853</v>
       </c>
       <c r="GK14" s="3" t="n">
-        <v>0.3125</v>
+        <v>0.2059</v>
       </c>
       <c r="GL14" s="3" t="n">
-        <v>0.1875</v>
+        <v>0.3089</v>
       </c>
       <c r="GM14" s="3" t="n">
-        <v>0.1352</v>
+        <v>0.1297</v>
       </c>
       <c r="GN14" s="3" t="n">
-        <v>0.1421</v>
+        <v>0.1732</v>
       </c>
       <c r="GO14" s="3" t="n">
-        <v>0.0089</v>
+        <v>0.0254</v>
       </c>
       <c r="GP14" s="3" t="n">
         <v>1</v>
@@ -12937,19 +12937,19 @@
         </is>
       </c>
       <c r="GR14" s="3" t="n">
-        <v>6.84</v>
+        <v>6.28</v>
       </c>
       <c r="GS14" s="3" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="GT14" s="3" t="n">
-        <v>11.53</v>
+        <v>11.3</v>
       </c>
       <c r="GU14" s="3" t="n">
-        <v>17.75</v>
+        <v>17.17</v>
       </c>
       <c r="GV14" s="3" t="n">
-        <v>4.63</v>
+        <v>4.21</v>
       </c>
       <c r="GW14" s="3" t="n">
         <v>0</v>
@@ -12960,88 +12960,88 @@
         </is>
       </c>
       <c r="GY14" s="3" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="GZ14" s="3" t="n">
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="HA14" s="3" t="n">
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="HB14" s="3" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="HC14" s="3" t="n">
-        <v>57.3</v>
+        <v>62.2</v>
       </c>
       <c r="HD14" s="3" t="n">
-        <v>57.3</v>
+        <v>59.2</v>
       </c>
       <c r="HE14" s="3" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="HF14" s="3" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="HG14" s="3" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="HH14" s="3" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="HI14" s="3" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="HJ14" s="3" t="n">
-        <v>34.8</v>
+        <v>33.4</v>
       </c>
       <c r="HK14" s="3" t="n">
-        <v>34.8</v>
+        <v>33.4</v>
       </c>
       <c r="HL14" s="3" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="HM14" s="3" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="HN14" s="3" t="n">
-        <v>28.1</v>
+        <v>26.9</v>
       </c>
       <c r="HO14" s="3" t="n">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="HP14" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="HQ14" s="3" t="n">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="HR14" s="3" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
       <c r="HS14" s="3" t="n">
-        <v>22.9</v>
+        <v>21.2</v>
       </c>
       <c r="HT14" s="3" t="n">
-        <v>22.9</v>
+        <v>17.5</v>
       </c>
       <c r="HU14" s="3" t="n">
-        <v>19.1</v>
+        <v>17.5</v>
       </c>
       <c r="HV14" s="3" t="n">
-        <v>19.1</v>
+        <v>16.7</v>
       </c>
       <c r="HW14" s="3" t="n">
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
       <c r="HX14" s="3" t="n">
-        <v>18.3</v>
+        <v>13.4</v>
       </c>
       <c r="HY14" s="3" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="HZ14" s="3" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="IA14" s="3" t="n">
         <v>8</v>
@@ -13426,13 +13426,13 @@
         <v>1.03</v>
       </c>
       <c r="CI15" s="3" t="n">
-        <v>85.2</v>
+        <v>86.3</v>
       </c>
       <c r="CJ15" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="CK15" s="3" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="CL15" s="3" t="n">
         <v>3</v>
@@ -14041,13 +14041,13 @@
         <v>6.17</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>6.17</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.846</v>
+        <v>0.845</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>6.8</v>
@@ -14083,10 +14083,10 @@
         <v>84.7</v>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AD16" s="5" t="n">
         <v>67.59999999999999</v>
@@ -14098,13 +14098,13 @@
         <v>55.4</v>
       </c>
       <c r="AG16" s="7" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="AH16" s="7" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="AI16" s="7" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="AJ16" s="8" t="n">
         <v>36.2</v>
@@ -14119,25 +14119,25 @@
         <v>31.7</v>
       </c>
       <c r="AN16" s="8" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="AO16" s="8" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="AP16" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="AQ16" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AR16" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AS16" s="8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AT16" s="8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AU16" s="8" t="n">
         <v>17.4</v>
@@ -14149,13 +14149,13 @@
         <v>16.1</v>
       </c>
       <c r="AX16" s="8" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="AY16" s="8" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="AZ16" s="3" t="n">
-        <v>199.51</v>
+        <v>199.49</v>
       </c>
       <c r="BA16" s="4" t="inlineStr">
         <is>
@@ -14644,13 +14644,13 @@
         <v>6.17</v>
       </c>
       <c r="GS16" s="3" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="GT16" s="3" t="n">
         <v>11.37</v>
       </c>
       <c r="GU16" s="3" t="n">
-        <v>16.45</v>
+        <v>16.44</v>
       </c>
       <c r="GV16" s="3" t="n">
         <v>4.29</v>
@@ -14673,10 +14673,10 @@
         <v>77.2</v>
       </c>
       <c r="HB16" s="3" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="HC16" s="3" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="HD16" s="3" t="n">
         <v>62.6</v>
@@ -14688,13 +14688,13 @@
         <v>51.4</v>
       </c>
       <c r="HG16" s="3" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="HH16" s="3" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="HI16" s="3" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="HJ16" s="3" t="n">
         <v>35.2</v>
@@ -14709,25 +14709,25 @@
         <v>31.7</v>
       </c>
       <c r="HN16" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="HO16" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="HP16" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="HQ16" s="3" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="HR16" s="3" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="HS16" s="3" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="HT16" s="3" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="HU16" s="3" t="n">
         <v>17.4</v>
@@ -14739,10 +14739,10 @@
         <v>16.1</v>
       </c>
       <c r="HX16" s="3" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="HY16" s="3" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="HZ16" s="3" t="n">
         <v>6.4</v>
@@ -14878,13 +14878,13 @@
         <v>8.210000000000001</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>6.99</v>
+        <v>6.98</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>6.99</v>
+        <v>6.98</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>5.98</v>
@@ -14893,13 +14893,13 @@
         <v>5.99</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6.11</v>
+        <v>6.09</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>5.99</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.981</v>
+        <v>0.984</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>14</v>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z17" s="5" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AA17" s="5" t="n">
         <v>72</v>
@@ -14938,19 +14938,19 @@
         <v>71.5</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="AF17" s="7" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="AG17" s="7" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="AH17" s="7" t="n">
         <v>40.9</v>
@@ -15007,7 +15007,7 @@
         <v>10.2</v>
       </c>
       <c r="AZ17" s="3" t="n">
-        <v>196.85</v>
+        <v>196.69</v>
       </c>
       <c r="BA17" s="4" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="BB17" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 65.9% | Edge +2.0</t>
+          <t>MORE 5.0 | 65.8% | Edge +2.0</t>
         </is>
       </c>
       <c r="BC17" s="4" t="inlineStr">
@@ -15028,13 +15028,13 @@
         <v>5</v>
       </c>
       <c r="BE17" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="BF17" s="3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BG17" s="3" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="BH17" s="4" t="inlineStr">
         <is>
@@ -15488,13 +15488,13 @@
         <v>5.99</v>
       </c>
       <c r="GS17" s="3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="GT17" s="3" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="GU17" s="3" t="n">
-        <v>15.83</v>
+        <v>15.86</v>
       </c>
       <c r="GV17" s="3" t="n">
         <v>4.24</v>
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="GY17" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="GZ17" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="HA17" s="3" t="n">
         <v>64.5</v>
@@ -15520,19 +15520,19 @@
         <v>64.5</v>
       </c>
       <c r="HC17" s="3" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="HD17" s="3" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="HE17" s="3" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="HF17" s="3" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="HG17" s="3" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="HH17" s="3" t="n">
         <v>37.9</v>
@@ -15722,10 +15722,10 @@
         <v>8.56</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>6.18</v>
@@ -15779,7 +15779,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>75.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AC18" s="5" t="n">
         <v>66.59999999999999</v>
@@ -15794,13 +15794,13 @@
         <v>54.6</v>
       </c>
       <c r="AG18" s="7" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="AH18" s="7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="AI18" s="8" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="AJ18" s="8" t="n">
         <v>33.7</v>
@@ -15809,10 +15809,10 @@
         <v>32.7</v>
       </c>
       <c r="AL18" s="8" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="AM18" s="8" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="AN18" s="8" t="n">
         <v>23.3</v>
@@ -15851,7 +15851,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AZ18" s="3" t="n">
-        <v>196.28</v>
+        <v>196.11</v>
       </c>
       <c r="BA18" s="4" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="BF18" s="3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BG18" s="3" t="n">
         <v>31.2</v>
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="GY18" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="GZ18" s="3" t="n">
         <v>75.90000000000001</v>
@@ -16369,7 +16369,7 @@
         <v>75.90000000000001</v>
       </c>
       <c r="HB18" s="3" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="HC18" s="3" t="n">
         <v>60.6</v>
@@ -16384,13 +16384,13 @@
         <v>50.6</v>
       </c>
       <c r="HG18" s="3" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="HH18" s="3" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="HI18" s="3" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="HJ18" s="3" t="n">
         <v>32.7</v>
@@ -16399,10 +16399,10 @@
         <v>32.7</v>
       </c>
       <c r="HL18" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="HM18" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="HN18" s="3" t="n">
         <v>23.3</v>
@@ -16441,7 +16441,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="HZ18" s="3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="IA18" s="3" t="n">
         <v>8</v>
@@ -16826,13 +16826,13 @@
         <v>1.03</v>
       </c>
       <c r="CI19" s="3" t="n">
-        <v>85.2</v>
+        <v>86.3</v>
       </c>
       <c r="CJ19" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="CK19" s="3" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="CL19" s="3" t="n">
         <v>3</v>
@@ -17145,7 +17145,7 @@
         <v>0.1339</v>
       </c>
       <c r="GD19" s="3" t="n">
-        <v>0.0479</v>
+        <v>0.0478</v>
       </c>
       <c r="GE19" s="3" t="n">
         <v>0.0049</v>
@@ -17426,10 +17426,10 @@
         <v>8.789999999999999</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>7.45</v>
+        <v>7.42</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>7.45</v>
+        <v>7.42</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>5.23</v>
@@ -17441,13 +17441,13 @@
         <v>6.56</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>6.56</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.904</v>
+        <v>0.906</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.800000000000001</v>
@@ -17474,37 +17474,37 @@
         </is>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z20" s="5" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AA20" s="5" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
       <c r="AD20" s="5" t="n">
-        <v>62.3</v>
+        <v>62.1</v>
       </c>
       <c r="AE20" s="6" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="AF20" s="7" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="AG20" s="7" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="AH20" s="7" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="AI20" s="8" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="AJ20" s="8" t="n">
         <v>34.1</v>
@@ -17513,16 +17513,16 @@
         <v>33.1</v>
       </c>
       <c r="AL20" s="8" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="AM20" s="8" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="AN20" s="8" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="AO20" s="8" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="AP20" s="8" t="n">
         <v>23.2</v>
@@ -17531,31 +17531,31 @@
         <v>23.2</v>
       </c>
       <c r="AR20" s="8" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AS20" s="8" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AT20" s="8" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AU20" s="8" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="AV20" s="8" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="AW20" s="8" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="AX20" s="8" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="AY20" s="8" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ20" s="3" t="n">
-        <v>191.89</v>
+        <v>191.44</v>
       </c>
       <c r="BA20" s="4" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="BB20" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 62.3% | Edge +2.5</t>
+          <t>MORE 5.0 | 62.1% | Edge +2.4</t>
         </is>
       </c>
       <c r="BC20" s="4" t="inlineStr">
@@ -17576,13 +17576,13 @@
         <v>5</v>
       </c>
       <c r="BE20" s="3" t="n">
-        <v>62.3</v>
+        <v>62.1</v>
       </c>
       <c r="BF20" s="3" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG20" s="3" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="BH20" s="4" t="inlineStr">
         <is>
@@ -18036,13 +18036,13 @@
         <v>6.56</v>
       </c>
       <c r="GS20" s="3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="GT20" s="3" t="n">
         <v>10.66</v>
       </c>
       <c r="GU20" s="3" t="n">
-        <v>16.99</v>
+        <v>17</v>
       </c>
       <c r="GV20" s="3" t="n">
         <v>4.41</v>
@@ -18056,37 +18056,37 @@
         </is>
       </c>
       <c r="GY20" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="GZ20" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="HA20" s="3" t="n">
-        <v>62.9</v>
+        <v>62.7</v>
       </c>
       <c r="HB20" s="3" t="n">
-        <v>62.9</v>
+        <v>62.7</v>
       </c>
       <c r="HC20" s="3" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="HD20" s="3" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="HE20" s="3" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="HF20" s="3" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="HG20" s="3" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="HH20" s="3" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="HI20" s="3" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="HJ20" s="3" t="n">
         <v>33.1</v>
@@ -18095,16 +18095,16 @@
         <v>33.1</v>
       </c>
       <c r="HL20" s="3" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="HM20" s="3" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="HN20" s="3" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="HO20" s="3" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="HP20" s="3" t="n">
         <v>23.2</v>
@@ -18113,25 +18113,25 @@
         <v>23.2</v>
       </c>
       <c r="HR20" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="HS20" s="3" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="HT20" s="3" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="HU20" s="3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="HV20" s="3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="HW20" s="3" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="HX20" s="3" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="HY20" s="3" t="n">
         <v>12.5</v>
@@ -18285,13 +18285,13 @@
         <v>6.53</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>6.53</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.925</v>
+        <v>0.927</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>7.6</v>
@@ -18336,10 +18336,10 @@
         <v>61.7</v>
       </c>
       <c r="AE21" s="6" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="AF21" s="7" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="AG21" s="7" t="n">
         <v>45.6</v>
@@ -18357,10 +18357,10 @@
         <v>31.1</v>
       </c>
       <c r="AL21" s="8" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="AM21" s="8" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="AN21" s="8" t="n">
         <v>24</v>
@@ -18384,7 +18384,7 @@
         <v>18.9</v>
       </c>
       <c r="AU21" s="8" t="n">
-        <v>15.1</v>
+        <v>18.9</v>
       </c>
       <c r="AV21" s="8" t="n">
         <v>15.1</v>
@@ -18396,7 +18396,7 @@
         <v>14.3</v>
       </c>
       <c r="AY21" s="8" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="AZ21" s="3" t="n">
         <v>190.99</v>
@@ -18888,13 +18888,13 @@
         <v>6.53</v>
       </c>
       <c r="GS21" s="3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="GT21" s="3" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="GU21" s="3" t="n">
-        <v>17.2</v>
+        <v>17.21</v>
       </c>
       <c r="GV21" s="3" t="n">
         <v>4.5</v>
@@ -18926,10 +18926,10 @@
         <v>56.7</v>
       </c>
       <c r="HE21" s="3" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="HF21" s="3" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="HG21" s="3" t="n">
         <v>42.1</v>
@@ -18947,10 +18947,10 @@
         <v>31.1</v>
       </c>
       <c r="HL21" s="3" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="HM21" s="3" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="HN21" s="3" t="n">
         <v>24</v>
@@ -18974,7 +18974,7 @@
         <v>18.9</v>
       </c>
       <c r="HU21" s="3" t="n">
-        <v>15.1</v>
+        <v>18.9</v>
       </c>
       <c r="HV21" s="3" t="n">
         <v>15.1</v>
@@ -18986,7 +18986,7 @@
         <v>14.3</v>
       </c>
       <c r="HY21" s="3" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="HZ21" s="3" t="n">
         <v>8</v>
@@ -19090,19 +19090,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>MIN @ CLE</t>
@@ -19110,148 +19110,148 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>7.15</v>
+        <v>6.89</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>7.15</v>
+        <v>6.89</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>5.39</v>
+        <v>5.23</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>5.83</v>
+        <v>5.81</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>7.19</v>
+        <v>6.71</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.819</v>
+        <v>0.877</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>5.4</v>
+        <v>8.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>7.53</v>
+        <v>8.27</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>7|7|10|5|3</t>
+          <t>12|8|16|3|5</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>7|7|10|5|3|3|2|5|12|0</t>
+          <t>12|8|16|3|5|0|21|6|5|9</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr">
         <is>
-          <t>7|7|10|5|3|3|2|5|12|0|5|10|7|35|2</t>
+          <t>12|8|16|3|5|0|21|6|5|9|18|0|3|11|7</t>
         </is>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>87</v>
+        <v>88.3</v>
       </c>
       <c r="Z22" s="5" t="n">
-        <v>78.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AA22" s="5" t="n">
-        <v>77.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AB22" s="5" t="n">
-        <v>65.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>64.3</v>
+        <v>62.1</v>
       </c>
       <c r="AD22" s="5" t="n">
-        <v>60.3</v>
+        <v>61.1</v>
       </c>
       <c r="AE22" s="6" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="AF22" s="7" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="AG22" s="7" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AH22" s="7" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
+      </c>
+      <c r="AH22" s="8" t="n">
+        <v>37.7</v>
       </c>
       <c r="AI22" s="8" t="n">
-        <v>38</v>
+        <v>37.2</v>
       </c>
       <c r="AJ22" s="8" t="n">
-        <v>32.6</v>
+        <v>31.2</v>
       </c>
       <c r="AK22" s="8" t="n">
-        <v>31.6</v>
+        <v>30.2</v>
       </c>
       <c r="AL22" s="8" t="n">
-        <v>28.2</v>
+        <v>26.5</v>
       </c>
       <c r="AM22" s="8" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="AN22" s="8" t="n">
-        <v>24.5</v>
+        <v>22.4</v>
       </c>
       <c r="AO22" s="8" t="n">
-        <v>22.8</v>
+        <v>20.5</v>
       </c>
       <c r="AP22" s="8" t="n">
-        <v>22.8</v>
+        <v>20.5</v>
       </c>
       <c r="AQ22" s="8" t="n">
-        <v>20.6</v>
+        <v>18.1</v>
       </c>
       <c r="AR22" s="8" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
       <c r="AS22" s="8" t="n">
-        <v>19.6</v>
+        <v>16.5</v>
       </c>
       <c r="AT22" s="8" t="n">
-        <v>15.7</v>
+        <v>16.5</v>
       </c>
       <c r="AU22" s="8" t="n">
-        <v>15.7</v>
+        <v>13.2</v>
       </c>
       <c r="AV22" s="8" t="n">
-        <v>15</v>
+        <v>12.2</v>
       </c>
       <c r="AW22" s="8" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="AX22" s="8" t="n">
-        <v>11.9</v>
+        <v>10.2</v>
       </c>
       <c r="AY22" s="8" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="AZ22" s="3" t="n">
-        <v>189.32</v>
+        <v>188.88</v>
       </c>
       <c r="BA22" s="4" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
       </c>
       <c r="BB22" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 60.3% | Edge +2.2</t>
+          <t>MORE 5.0 | 61.1% | Edge +1.9</t>
         </is>
       </c>
       <c r="BC22" s="4" t="inlineStr">
@@ -19272,13 +19272,13 @@
         <v>5</v>
       </c>
       <c r="BE22" s="3" t="n">
-        <v>60.3</v>
+        <v>61.1</v>
       </c>
       <c r="BF22" s="3" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="BG22" s="3" t="n">
-        <v>20.6</v>
+        <v>22.2</v>
       </c>
       <c r="BH22" s="4" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         </is>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ22" s="4" t="inlineStr">
         <is>
@@ -19295,14 +19295,14 @@
       </c>
       <c r="BK22" s="4" t="n"/>
       <c r="BL22" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM22" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN22" s="4" t="inlineStr">
         <is>
-          <t>4-4-4-3-3-3-3</t>
+          <t>4-2-4-4-2-2-2</t>
         </is>
       </c>
       <c r="BO22" s="3" t="n">
@@ -19312,7 +19312,7 @@
         <v>97</v>
       </c>
       <c r="BQ22" s="3" t="n">
-        <v>4.92</v>
+        <v>5.02</v>
       </c>
       <c r="BR22" s="4" t="inlineStr">
         <is>
@@ -19320,14 +19320,14 @@
         </is>
       </c>
       <c r="BS22" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BT22" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="BU22" s="4" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="BV22" s="4" t="inlineStr">
@@ -19336,31 +19336,31 @@
         </is>
       </c>
       <c r="BW22" s="3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX22" s="3" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BY22" s="3" t="n">
-        <v>0.2062</v>
+        <v>0.2018</v>
       </c>
       <c r="BZ22" s="3" t="n">
-        <v>0.0412</v>
+        <v>0.0351</v>
       </c>
       <c r="CA22" s="3" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="CB22" s="3" t="n">
-        <v>3.74</v>
+        <v>4.77</v>
       </c>
       <c r="CC22" s="3" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="CD22" s="3" t="n">
-        <v>0.2123</v>
+        <v>0.2253</v>
       </c>
       <c r="CE22" s="3" t="n">
-        <v>0.0304</v>
+        <v>0.0314</v>
       </c>
       <c r="CF22" s="4" t="inlineStr">
         <is>
@@ -19374,13 +19374,13 @@
         <v>1</v>
       </c>
       <c r="CI22" s="3" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="CJ22" s="3" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CK22" s="3" t="n">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="CL22" s="3" t="n">
         <v>0</v>
@@ -19391,69 +19391,69 @@
         </is>
       </c>
       <c r="CN22" s="3" t="n">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="CO22" s="3" t="n">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="CP22" s="3" t="n">
-        <v>0.251</v>
+        <v>0.275</v>
       </c>
       <c r="CQ22" s="3" t="n">
-        <v>0.308</v>
+        <v>0.338</v>
       </c>
       <c r="CR22" s="3" t="n">
-        <v>0.425</v>
+        <v>0.409</v>
       </c>
       <c r="CS22" s="3" t="n">
-        <v>0.733</v>
+        <v>0.747</v>
       </c>
       <c r="CT22" s="3" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="CU22" s="3" t="n">
-        <v>0.741</v>
+        <v>0.786</v>
       </c>
       <c r="CV22" s="3" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="CW22" s="3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="CX22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CY22" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CZ22" s="3" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="DA22" s="3" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="DB22" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="DC22" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="DD22" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="DE22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Cleveland Guardians: 7 FS|2026-07-21 @ Cleveland Guardians: 7 FS|2026-07-20 @ Cleveland Guardians: 10 FS|2026-07-19 @ Chicago Cubs: 5 FS|2026-07-18 @ Chicago Cubs: 3 FS</t>
+          <t>2026-07-22 vs Minnesota Twins: 12 FS|2026-07-21 vs Minnesota Twins: 8 FS|2026-07-20 vs Minnesota Twins: 16 FS|2026-07-19 vs Pittsburgh Pirates: 3 FS|2026-07-18 vs Pittsburgh Pirates: 5 FS</t>
         </is>
       </c>
       <c r="DF22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Cleveland Guardians: 7 FS|2026-07-21 @ Cleveland Guardians: 7 FS|2026-07-20 @ Cleveland Guardians: 10 FS|2026-07-19 @ Chicago Cubs: 5 FS|2026-07-18 @ Chicago Cubs: 3 FS|2026-07-17 @ Chicago Cubs: 3 FS|2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 5 FS|2026-07-10 vs Los Angeles Angels: 12 FS|2026-07-09 vs Cleveland Guardians: 0 FS</t>
+          <t>2026-07-22 vs Minnesota Twins: 12 FS|2026-07-21 vs Minnesota Twins: 8 FS|2026-07-20 vs Minnesota Twins: 16 FS|2026-07-19 vs Pittsburgh Pirates: 3 FS|2026-07-18 vs Pittsburgh Pirates: 5 FS|2026-07-18 vs Pittsburgh Pirates: 0 FS|2026-07-12 @ Miami Marlins: 21 FS|2026-07-11 @ Miami Marlins: 6 FS|2026-07-10 @ Miami Marlins: 5 FS|2026-07-09 @ Minnesota Twins: 9 FS</t>
         </is>
       </c>
       <c r="DG22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Cleveland Guardians: 7 FS|2026-07-21 @ Cleveland Guardians: 7 FS|2026-07-20 @ Cleveland Guardians: 10 FS|2026-07-19 @ Chicago Cubs: 5 FS|2026-07-18 @ Chicago Cubs: 3 FS|2026-07-17 @ Chicago Cubs: 3 FS|2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 5 FS|2026-07-10 vs Los Angeles Angels: 12 FS|2026-07-09 vs Cleveland Guardians: 0 FS|2026-07-08 vs Cleveland Guardians: 5 FS|2026-07-07 vs Cleveland Guardians: 10 FS|2026-07-05 @ New York Yankees: 7 FS|2026-07-04 @ New York Yankees: 35 FS|2026-07-03 @ New York Yankees: 2 FS</t>
+          <t>2026-07-22 vs Minnesota Twins: 12 FS|2026-07-21 vs Minnesota Twins: 8 FS|2026-07-20 vs Minnesota Twins: 16 FS|2026-07-19 vs Pittsburgh Pirates: 3 FS|2026-07-18 vs Pittsburgh Pirates: 5 FS|2026-07-18 vs Pittsburgh Pirates: 0 FS|2026-07-12 @ Miami Marlins: 21 FS|2026-07-11 @ Miami Marlins: 6 FS|2026-07-10 @ Miami Marlins: 5 FS|2026-07-09 @ Minnesota Twins: 9 FS|2026-07-08 @ Minnesota Twins: 18 FS|2026-07-07 @ Minnesota Twins: 0 FS|2026-07-05 vs Chicago White Sox: 3 FS|2026-07-04 vs Chicago White Sox: 11 FS|2026-07-03 vs Chicago White Sox: 7 FS</t>
         </is>
       </c>
       <c r="DH22" s="3" t="n">
@@ -19463,10 +19463,10 @@
         <v>30</v>
       </c>
       <c r="DJ22" s="3" t="n">
-        <v>8.869999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="DK22" s="3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="DL22" s="4" t="inlineStr">
         <is>
@@ -19474,10 +19474,10 @@
         </is>
       </c>
       <c r="DM22" s="3" t="n">
-        <v>5.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DN22" s="3" t="n">
-        <v>7.93</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DO22" s="3" t="n">
         <v>0.304</v>
@@ -19488,40 +19488,40 @@
         </is>
       </c>
       <c r="DQ22" s="3" t="n">
-        <v>8.869999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="DR22" s="3" t="n">
-        <v>1.85</v>
+        <v>2.053</v>
       </c>
       <c r="DS22" s="3" t="n">
-        <v>0.2833</v>
+        <v>0.2982</v>
       </c>
       <c r="DT22" s="3" t="n">
-        <v>0.1333</v>
+        <v>0.0877</v>
       </c>
       <c r="DU22" s="3" t="n">
-        <v>0.0333</v>
+        <v>0.0526</v>
       </c>
       <c r="DV22" s="3" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="DW22" s="3" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="DX22" s="3" t="n">
-        <v>8.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DY22" s="3" t="n">
-        <v>9.609999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="DZ22" s="3" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="EA22" s="3" t="n">
-        <v>7.93</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="EB22" s="3" t="n">
-        <v>7.79</v>
+        <v>7.45</v>
       </c>
       <c r="EC22" s="3" t="n">
         <v>28</v>
@@ -19539,25 +19539,25 @@
         <v>20</v>
       </c>
       <c r="EH22" s="3" t="n">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="EI22" s="3" t="n">
-        <v>82.79000000000001</v>
+        <v>81.38</v>
       </c>
       <c r="EJ22" s="3" t="n">
-        <v>24.23</v>
+        <v>20.93</v>
       </c>
       <c r="EK22" s="3" t="n">
-        <v>1.37</v>
+        <v>0.78</v>
       </c>
       <c r="EL22" s="3" t="n">
-        <v>26.96</v>
+        <v>32.17</v>
       </c>
       <c r="EM22" s="3" t="n">
-        <v>0.404</v>
+        <v>0.315</v>
       </c>
       <c r="EN22" s="3" t="n">
-        <v>0.9236</v>
+        <v>0.8256</v>
       </c>
       <c r="EO22" s="3" t="n">
         <v>1</v>
@@ -19569,10 +19569,10 @@
         <v>1</v>
       </c>
       <c r="ER22" s="3" t="n">
-        <v>0.9953</v>
+        <v>0.9628</v>
       </c>
       <c r="ES22" s="3" t="n">
-        <v>528</v>
+        <v>339</v>
       </c>
       <c r="ET22" s="4" t="inlineStr">
         <is>
@@ -19580,10 +19580,10 @@
         </is>
       </c>
       <c r="EU22" s="3" t="n">
-        <v>1.14</v>
+        <v>1.069</v>
       </c>
       <c r="EV22" s="3" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="EW22" s="4" t="inlineStr">
         <is>
@@ -19591,52 +19591,52 @@
         </is>
       </c>
       <c r="EX22" s="3" t="n">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="EY22" s="3" t="n">
-        <v>82.79000000000001</v>
+        <v>81.38</v>
       </c>
       <c r="EZ22" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FA22" s="3" t="n">
-        <v>17.47</v>
+        <v>17.53</v>
       </c>
       <c r="FB22" s="3" t="n">
-        <v>34.13</v>
+        <v>33.61</v>
       </c>
       <c r="FC22" s="3" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="FD22" s="3" t="n">
-        <v>67.2</v>
+        <v>58.9</v>
       </c>
       <c r="FE22" s="3" t="n">
-        <v>20.1</v>
+        <v>26.7</v>
       </c>
       <c r="FF22" s="3" t="n">
-        <v>0.9762</v>
+        <v>0.978</v>
       </c>
       <c r="FG22" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.9943</v>
       </c>
       <c r="FH22" s="3" t="n">
-        <v>0.9695</v>
+        <v>0.9578</v>
       </c>
       <c r="FI22" s="3" t="n">
-        <v>0.9963</v>
+        <v>0.9887</v>
       </c>
       <c r="FJ22" s="3" t="n">
-        <v>0.9641</v>
+        <v>0.9412</v>
       </c>
       <c r="FK22" s="3" t="n">
-        <v>0.9796</v>
+        <v>1.0115</v>
       </c>
       <c r="FL22" s="3" t="n">
-        <v>7.16</v>
+        <v>8.59</v>
       </c>
       <c r="FM22" s="3" t="n">
-        <v>-1.7</v>
+        <v>0.95</v>
       </c>
       <c r="FN22" s="4" t="inlineStr">
         <is>
@@ -19681,52 +19681,52 @@
         <v>27</v>
       </c>
       <c r="FZ22" s="3" t="n">
-        <v>0.8625</v>
+        <v>1.3</v>
       </c>
       <c r="GA22" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GB22" s="3" t="n">
-        <v>0.9842</v>
+        <v>0.9961</v>
       </c>
       <c r="GC22" s="3" t="n">
-        <v>0.1269</v>
+        <v>0.1503</v>
       </c>
       <c r="GD22" s="3" t="n">
-        <v>0.0488</v>
+        <v>0.0322</v>
       </c>
       <c r="GE22" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="GF22" s="3" t="n">
-        <v>0.036</v>
+        <v>0.0259</v>
       </c>
       <c r="GG22" s="3" t="n">
-        <v>0.076</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="GH22" s="3" t="n">
-        <v>0.0076</v>
+        <v>0.0124</v>
       </c>
       <c r="GI22" s="3" t="n">
-        <v>0.2408</v>
+        <v>0.1822</v>
       </c>
       <c r="GJ22" s="3" t="n">
-        <v>0.4692</v>
+        <v>0.4015</v>
       </c>
       <c r="GK22" s="3" t="n">
-        <v>0.2847</v>
+        <v>0.2879</v>
       </c>
       <c r="GL22" s="3" t="n">
-        <v>0.2461</v>
+        <v>0.3106</v>
       </c>
       <c r="GM22" s="3" t="n">
-        <v>0.1178</v>
+        <v>0.1217</v>
       </c>
       <c r="GN22" s="3" t="n">
-        <v>0.1426</v>
+        <v>0.1285</v>
       </c>
       <c r="GO22" s="3" t="n">
-        <v>0.0071</v>
+        <v>0.0211</v>
       </c>
       <c r="GP22" s="3" t="n">
         <v>1</v>
@@ -19737,19 +19737,19 @@
         </is>
       </c>
       <c r="GR22" s="3" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="GS22" s="3" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="GT22" s="3" t="n">
-        <v>9.48</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="GU22" s="3" t="n">
-        <v>16.04</v>
+        <v>15.75</v>
       </c>
       <c r="GV22" s="3" t="n">
-        <v>4.54</v>
+        <v>4.67</v>
       </c>
       <c r="GW22" s="3" t="n">
         <v>0</v>
@@ -19760,88 +19760,88 @@
         </is>
       </c>
       <c r="GY22" s="3" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="GZ22" s="3" t="n">
-        <v>70.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="HA22" s="3" t="n">
-        <v>70.2</v>
+        <v>60.1</v>
       </c>
       <c r="HB22" s="3" t="n">
-        <v>58.3</v>
+        <v>60.1</v>
       </c>
       <c r="HC22" s="3" t="n">
-        <v>58.3</v>
+        <v>56.1</v>
       </c>
       <c r="HD22" s="3" t="n">
-        <v>55.3</v>
+        <v>56.1</v>
       </c>
       <c r="HE22" s="3" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="HF22" s="3" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="HG22" s="3" t="n">
-        <v>42.1</v>
+        <v>41.1</v>
       </c>
       <c r="HH22" s="3" t="n">
-        <v>42.1</v>
+        <v>34.7</v>
       </c>
       <c r="HI22" s="3" t="n">
-        <v>35.5</v>
+        <v>34.7</v>
       </c>
       <c r="HJ22" s="3" t="n">
-        <v>31.6</v>
+        <v>30.2</v>
       </c>
       <c r="HK22" s="3" t="n">
-        <v>31.6</v>
+        <v>30.2</v>
       </c>
       <c r="HL22" s="3" t="n">
-        <v>28.2</v>
+        <v>26.5</v>
       </c>
       <c r="HM22" s="3" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="HN22" s="3" t="n">
-        <v>24.5</v>
+        <v>22.4</v>
       </c>
       <c r="HO22" s="3" t="n">
-        <v>22.8</v>
+        <v>20.5</v>
       </c>
       <c r="HP22" s="3" t="n">
-        <v>22.8</v>
+        <v>20.5</v>
       </c>
       <c r="HQ22" s="3" t="n">
-        <v>20.6</v>
+        <v>18.1</v>
       </c>
       <c r="HR22" s="3" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
       <c r="HS22" s="3" t="n">
-        <v>19.6</v>
+        <v>16.5</v>
       </c>
       <c r="HT22" s="3" t="n">
-        <v>15.7</v>
+        <v>16.5</v>
       </c>
       <c r="HU22" s="3" t="n">
-        <v>15.7</v>
+        <v>13.2</v>
       </c>
       <c r="HV22" s="3" t="n">
-        <v>15</v>
+        <v>12.2</v>
       </c>
       <c r="HW22" s="3" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="HX22" s="3" t="n">
-        <v>11.9</v>
+        <v>10.2</v>
       </c>
       <c r="HY22" s="3" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="HZ22" s="3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="IA22" s="3" t="n">
         <v>8</v>
@@ -19942,168 +19942,168 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>SD @ ATL</t>
+          <t>MIN @ CLE</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>8.109999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.82</v>
+        <v>7.07</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>6.82</v>
+        <v>7.07</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5.23</v>
+        <v>5.37</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>5.48</v>
+        <v>5.83</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>5.68</v>
+        <v>5.89</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>6.51</v>
+        <v>7.17</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.68</v>
+        <v>5.89</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.873</v>
+        <v>0.821</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>7.33</v>
+        <v>7.53</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>10|4|2|2|12</t>
+          <t>7|7|10|5|3</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>10|4|2|2|12|8|5|14|0|5</t>
+          <t>7|7|10|5|3|3|2|5|12|0</t>
         </is>
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>10|4|2|2|12|8|5|14|0|5|0|10|5|13|20</t>
+          <t>7|7|10|5|3|3|2|5|12|0|5|10|7|35|2</t>
         </is>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>88.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Z23" s="5" t="n">
-        <v>79.8</v>
+        <v>77.7</v>
       </c>
       <c r="AA23" s="5" t="n">
-        <v>69.5</v>
+        <v>77.2</v>
       </c>
       <c r="AB23" s="5" t="n">
-        <v>69</v>
+        <v>65.3</v>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>63.5</v>
+        <v>64.3</v>
       </c>
       <c r="AD23" s="5" t="n">
-        <v>62.5</v>
+        <v>60.2</v>
       </c>
       <c r="AE23" s="6" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="AF23" s="7" t="n">
-        <v>50.3</v>
+        <v>48.7</v>
       </c>
       <c r="AG23" s="7" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="AH23" s="8" t="n">
-        <v>38.1</v>
+        <v>44.9</v>
+      </c>
+      <c r="AH23" s="7" t="n">
+        <v>44.4</v>
       </c>
       <c r="AI23" s="8" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="AJ23" s="8" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="AL23" s="8" t="n">
-        <v>26.4</v>
+        <v>27.4</v>
       </c>
       <c r="AM23" s="8" t="n">
-        <v>26.4</v>
+        <v>24</v>
       </c>
       <c r="AN23" s="8" t="n">
-        <v>22.2</v>
+        <v>24</v>
       </c>
       <c r="AO23" s="8" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="AP23" s="8" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="AQ23" s="8" t="n">
-        <v>16.7</v>
+        <v>20.2</v>
       </c>
       <c r="AR23" s="8" t="n">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="AS23" s="8" t="n">
-        <v>15.3</v>
+        <v>19</v>
       </c>
       <c r="AT23" s="8" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="AU23" s="8" t="n">
-        <v>12.3</v>
+        <v>15.4</v>
       </c>
       <c r="AV23" s="8" t="n">
-        <v>11.3</v>
+        <v>14.6</v>
       </c>
       <c r="AW23" s="8" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="AX23" s="8" t="n">
-        <v>9.1</v>
+        <v>11.5</v>
       </c>
       <c r="AY23" s="8" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="AZ23" s="3" t="n">
-        <v>187.06</v>
+        <v>187.96</v>
       </c>
       <c r="BA23" s="4" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="BB23" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 62.5% | Edge +1.8</t>
+          <t>MORE 5.0 | 60.2% | Edge +2.1</t>
         </is>
       </c>
       <c r="BC23" s="4" t="inlineStr">
@@ -20124,21 +20124,21 @@
         <v>5</v>
       </c>
       <c r="BE23" s="3" t="n">
-        <v>62.5</v>
+        <v>60.2</v>
       </c>
       <c r="BF23" s="3" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="BG23" s="3" t="n">
-        <v>25</v>
+        <v>20.4</v>
       </c>
       <c r="BH23" s="4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Playable</t>
         </is>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ23" s="4" t="inlineStr">
         <is>
@@ -20147,14 +20147,14 @@
       </c>
       <c r="BK23" s="4" t="n"/>
       <c r="BL23" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BM23" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN23" s="4" t="inlineStr">
         <is>
-          <t>7-6-6-5-5-5-5</t>
+          <t>4-4-4-3-3-3-3</t>
         </is>
       </c>
       <c r="BO23" s="3" t="n">
@@ -20164,7 +20164,7 @@
         <v>97</v>
       </c>
       <c r="BQ23" s="3" t="n">
-        <v>4.61</v>
+        <v>4.92</v>
       </c>
       <c r="BR23" s="4" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="BU23" s="4" t="inlineStr">
         <is>
-          <t>Griffin Canning</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="BV23" s="4" t="inlineStr">
@@ -20188,124 +20188,124 @@
         </is>
       </c>
       <c r="BW23" s="3" t="n">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="BX23" s="3" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="BY23" s="3" t="n">
-        <v>0.2415</v>
+        <v>0.2062</v>
       </c>
       <c r="BZ23" s="3" t="n">
-        <v>0.034</v>
+        <v>0.0412</v>
       </c>
       <c r="CA23" s="3" t="n">
-        <v>0.1208</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="CB23" s="3" t="n">
-        <v>4.24</v>
+        <v>3.74</v>
       </c>
       <c r="CC23" s="3" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="CD23" s="3" t="n">
-        <v>0.2194</v>
+        <v>0.2123</v>
       </c>
       <c r="CE23" s="3" t="n">
-        <v>0.0292</v>
+        <v>0.0304</v>
       </c>
       <c r="CF23" s="4" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="CG23" s="3" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="CH23" s="3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="CI23" s="3" t="n">
-        <v>85.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="CJ23" s="3" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CK23" s="3" t="n">
-        <v>226</v>
+        <v>327</v>
       </c>
       <c r="CL23" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CM23" s="4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="CN23" s="3" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CO23" s="3" t="n">
         <v>367</v>
       </c>
       <c r="CP23" s="3" t="n">
-        <v>0.264</v>
+        <v>0.251</v>
       </c>
       <c r="CQ23" s="3" t="n">
-        <v>0.316</v>
+        <v>0.308</v>
       </c>
       <c r="CR23" s="3" t="n">
-        <v>0.414</v>
+        <v>0.425</v>
       </c>
       <c r="CS23" s="3" t="n">
-        <v>0.73</v>
+        <v>0.733</v>
       </c>
       <c r="CT23" s="3" t="n">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="CU23" s="3" t="n">
-        <v>0.743</v>
+        <v>0.741</v>
       </c>
       <c r="CV23" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="CW23" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CX23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CY23" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CZ23" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="DA23" s="3" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="DB23" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="DC23" s="3" t="n">
         <v>2</v>
       </c>
       <c r="DD23" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DE23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs San Diego Padres: 10 FS|2026-07-21 vs San Diego Padres: 4 FS|2026-07-20 vs San Diego Padres: 2 FS|2026-07-19 vs Texas Rangers: 2 FS|2026-07-18 vs Texas Rangers: 12 FS</t>
+          <t>2026-07-22 @ Cleveland Guardians: 7 FS|2026-07-21 @ Cleveland Guardians: 7 FS|2026-07-20 @ Cleveland Guardians: 10 FS|2026-07-19 @ Chicago Cubs: 5 FS|2026-07-18 @ Chicago Cubs: 3 FS</t>
         </is>
       </c>
       <c r="DF23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs San Diego Padres: 10 FS|2026-07-21 vs San Diego Padres: 4 FS|2026-07-20 vs San Diego Padres: 2 FS|2026-07-19 vs Texas Rangers: 2 FS|2026-07-18 vs Texas Rangers: 12 FS|2026-07-17 vs Texas Rangers: 8 FS|2026-07-12 @ St. Louis Cardinals: 5 FS|2026-07-11 @ St. Louis Cardinals: 14 FS|2026-07-10 @ St. Louis Cardinals: 0 FS|2026-07-09 @ Pittsburgh Pirates: 5 FS</t>
+          <t>2026-07-22 @ Cleveland Guardians: 7 FS|2026-07-21 @ Cleveland Guardians: 7 FS|2026-07-20 @ Cleveland Guardians: 10 FS|2026-07-19 @ Chicago Cubs: 5 FS|2026-07-18 @ Chicago Cubs: 3 FS|2026-07-17 @ Chicago Cubs: 3 FS|2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 5 FS|2026-07-10 vs Los Angeles Angels: 12 FS|2026-07-09 vs Cleveland Guardians: 0 FS</t>
         </is>
       </c>
       <c r="DG23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs San Diego Padres: 10 FS|2026-07-21 vs San Diego Padres: 4 FS|2026-07-20 vs San Diego Padres: 2 FS|2026-07-19 vs Texas Rangers: 2 FS|2026-07-18 vs Texas Rangers: 12 FS|2026-07-17 vs Texas Rangers: 8 FS|2026-07-12 @ St. Louis Cardinals: 5 FS|2026-07-11 @ St. Louis Cardinals: 14 FS|2026-07-10 @ St. Louis Cardinals: 0 FS|2026-07-09 @ Pittsburgh Pirates: 5 FS|2026-07-08 @ Pittsburgh Pirates: 0 FS|2026-07-07 @ Pittsburgh Pirates: 10 FS|2026-07-06 vs New York Mets: 5 FS|2026-07-05 vs New York Mets: 13 FS|2026-07-04 vs New York Mets: 20 FS</t>
+          <t>2026-07-22 @ Cleveland Guardians: 7 FS|2026-07-21 @ Cleveland Guardians: 7 FS|2026-07-20 @ Cleveland Guardians: 10 FS|2026-07-19 @ Chicago Cubs: 5 FS|2026-07-18 @ Chicago Cubs: 3 FS|2026-07-17 @ Chicago Cubs: 3 FS|2026-07-12 vs Los Angeles Angels: 2 FS|2026-07-11 vs Los Angeles Angels: 5 FS|2026-07-10 vs Los Angeles Angels: 12 FS|2026-07-09 vs Cleveland Guardians: 0 FS|2026-07-08 vs Cleveland Guardians: 5 FS|2026-07-07 vs Cleveland Guardians: 10 FS|2026-07-05 @ New York Yankees: 7 FS|2026-07-04 @ New York Yankees: 35 FS|2026-07-03 @ New York Yankees: 2 FS</t>
         </is>
       </c>
       <c r="DH23" s="3" t="n">
@@ -20315,10 +20315,10 @@
         <v>30</v>
       </c>
       <c r="DJ23" s="3" t="n">
-        <v>7.97</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DK23" s="3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="DL23" s="4" t="inlineStr">
         <is>
@@ -20326,54 +20326,54 @@
         </is>
       </c>
       <c r="DM23" s="3" t="n">
-        <v>6.14</v>
+        <v>5.29</v>
       </c>
       <c r="DN23" s="3" t="n">
-        <v>6.43</v>
+        <v>7.93</v>
       </c>
       <c r="DO23" s="3" t="n">
-        <v>0.237</v>
+        <v>0.304</v>
       </c>
       <c r="DP23" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="DQ23" s="3" t="n">
-        <v>7.97</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DR23" s="3" t="n">
-        <v>1.452</v>
+        <v>1.85</v>
       </c>
       <c r="DS23" s="3" t="n">
-        <v>0.2258</v>
+        <v>0.2833</v>
       </c>
       <c r="DT23" s="3" t="n">
-        <v>0.0806</v>
+        <v>0.1333</v>
       </c>
       <c r="DU23" s="3" t="n">
-        <v>0.0161</v>
+        <v>0.0333</v>
       </c>
       <c r="DV23" s="3" t="n">
-        <v>0.0161</v>
+        <v>0.0667</v>
       </c>
       <c r="DW23" s="3" t="n">
-        <v>0.0161</v>
+        <v>0</v>
       </c>
       <c r="DX23" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="DY23" s="3" t="n">
-        <v>8.69</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ23" s="3" t="n">
-        <v>7.87</v>
+        <v>8.66</v>
       </c>
       <c r="EA23" s="3" t="n">
-        <v>8.01</v>
+        <v>7.94</v>
       </c>
       <c r="EB23" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="EC23" s="3" t="n">
         <v>28</v>
@@ -20391,25 +20391,25 @@
         <v>20</v>
       </c>
       <c r="EH23" s="3" t="n">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="EI23" s="3" t="n">
-        <v>80.26000000000001</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="EJ23" s="3" t="n">
-        <v>19.11</v>
+        <v>24.23</v>
       </c>
       <c r="EK23" s="3" t="n">
-        <v>0.32</v>
+        <v>1.37</v>
       </c>
       <c r="EL23" s="3" t="n">
-        <v>31.21</v>
+        <v>26.96</v>
       </c>
       <c r="EM23" s="3" t="n">
-        <v>0.34</v>
+        <v>0.404</v>
       </c>
       <c r="EN23" s="3" t="n">
-        <v>0.8218</v>
+        <v>0.9236</v>
       </c>
       <c r="EO23" s="3" t="n">
         <v>1</v>
@@ -20421,10 +20421,10 @@
         <v>1</v>
       </c>
       <c r="ER23" s="3" t="n">
-        <v>1.0107</v>
+        <v>0.9953</v>
       </c>
       <c r="ES23" s="3" t="n">
-        <v>600</v>
+        <v>528</v>
       </c>
       <c r="ET23" s="4" t="inlineStr">
         <is>
@@ -20432,63 +20432,63 @@
         </is>
       </c>
       <c r="EU23" s="3" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="EV23" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="EW23" s="4" t="inlineStr">
         <is>
-          <t>Fallback</t>
+          <t>Statcast</t>
         </is>
       </c>
       <c r="EX23" s="3" t="n">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="EY23" s="3" t="n">
-        <v>80.26000000000001</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="EZ23" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FA23" s="3" t="n">
-        <v>22.14</v>
+        <v>17.47</v>
       </c>
       <c r="FB23" s="3" t="n">
-        <v>31.36</v>
+        <v>34.13</v>
       </c>
       <c r="FC23" s="3" t="n">
-        <v>15.9</v>
+        <v>12.6</v>
       </c>
       <c r="FD23" s="3" t="n">
         <v>67.2</v>
       </c>
       <c r="FE23" s="3" t="n">
-        <v>16.9</v>
+        <v>20.1</v>
       </c>
       <c r="FF23" s="3" t="n">
-        <v>1.0307</v>
+        <v>0.9781</v>
       </c>
       <c r="FG23" s="3" t="n">
-        <v>0.9933</v>
+        <v>0.9981</v>
       </c>
       <c r="FH23" s="3" t="n">
-        <v>1.0054</v>
+        <v>0.9714</v>
       </c>
       <c r="FI23" s="3" t="n">
-        <v>0.9866</v>
+        <v>0.9963</v>
       </c>
       <c r="FJ23" s="3" t="n">
-        <v>0.9847</v>
+        <v>0.9659</v>
       </c>
       <c r="FK23" s="3" t="n">
-        <v>0.9873</v>
+        <v>0.9796</v>
       </c>
       <c r="FL23" s="3" t="n">
-        <v>6.91</v>
+        <v>7.16</v>
       </c>
       <c r="FM23" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.7</v>
       </c>
       <c r="FN23" s="4" t="inlineStr">
         <is>
@@ -20533,52 +20533,52 @@
         <v>27</v>
       </c>
       <c r="FZ23" s="3" t="n">
-        <v>0.9916</v>
+        <v>0.8625</v>
       </c>
       <c r="GA23" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GB23" s="3" t="n">
-        <v>1</v>
+        <v>0.9849</v>
       </c>
       <c r="GC23" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1269</v>
       </c>
       <c r="GD23" s="3" t="n">
-        <v>0.048</v>
+        <v>0.0489</v>
       </c>
       <c r="GE23" s="3" t="n">
-        <v>0.0041</v>
+        <v>0.0032</v>
       </c>
       <c r="GF23" s="3" t="n">
-        <v>0.0244</v>
+        <v>0.0361</v>
       </c>
       <c r="GG23" s="3" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="GH23" s="3" t="n">
-        <v>0.0101</v>
+        <v>0.0076</v>
       </c>
       <c r="GI23" s="3" t="n">
-        <v>0.174</v>
+        <v>0.2408</v>
       </c>
       <c r="GJ23" s="3" t="n">
-        <v>0.4927</v>
+        <v>0.4692</v>
       </c>
       <c r="GK23" s="3" t="n">
-        <v>0.2536</v>
+        <v>0.2847</v>
       </c>
       <c r="GL23" s="3" t="n">
-        <v>0.2536</v>
+        <v>0.2461</v>
       </c>
       <c r="GM23" s="3" t="n">
-        <v>0.122</v>
+        <v>0.1178</v>
       </c>
       <c r="GN23" s="3" t="n">
-        <v>0.1416</v>
+        <v>0.1426</v>
       </c>
       <c r="GO23" s="3" t="n">
-        <v>0.0117</v>
+        <v>0.0071</v>
       </c>
       <c r="GP23" s="3" t="n">
         <v>1</v>
@@ -20589,19 +20589,19 @@
         </is>
       </c>
       <c r="GR23" s="3" t="n">
-        <v>5.68</v>
+        <v>5.89</v>
       </c>
       <c r="GS23" s="3" t="n">
-        <v>2.61</v>
+        <v>2.91</v>
       </c>
       <c r="GT23" s="3" t="n">
-        <v>9.6</v>
+        <v>9.48</v>
       </c>
       <c r="GU23" s="3" t="n">
-        <v>14.83</v>
+        <v>16.04</v>
       </c>
       <c r="GV23" s="3" t="n">
-        <v>4.23</v>
+        <v>4.54</v>
       </c>
       <c r="GW23" s="3" t="n">
         <v>0</v>
@@ -20612,85 +20612,85 @@
         </is>
       </c>
       <c r="GY23" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="GZ23" s="3" t="n">
-        <v>71.8</v>
+        <v>69.7</v>
       </c>
       <c r="HA23" s="3" t="n">
-        <v>62</v>
+        <v>69.7</v>
       </c>
       <c r="HB23" s="3" t="n">
-        <v>62</v>
+        <v>58.3</v>
       </c>
       <c r="HC23" s="3" t="n">
-        <v>57.5</v>
+        <v>58.3</v>
       </c>
       <c r="HD23" s="3" t="n">
-        <v>57.5</v>
+        <v>55.2</v>
       </c>
       <c r="HE23" s="3" t="n">
-        <v>46.3</v>
+        <v>44.7</v>
       </c>
       <c r="HF23" s="3" t="n">
-        <v>46.3</v>
+        <v>44.7</v>
       </c>
       <c r="HG23" s="3" t="n">
-        <v>42.9</v>
+        <v>41.4</v>
       </c>
       <c r="HH23" s="3" t="n">
-        <v>35.1</v>
+        <v>41.4</v>
       </c>
       <c r="HI23" s="3" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="HJ23" s="3" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="HK23" s="3" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="HL23" s="3" t="n">
-        <v>26.4</v>
+        <v>27.4</v>
       </c>
       <c r="HM23" s="3" t="n">
-        <v>26.4</v>
+        <v>24</v>
       </c>
       <c r="HN23" s="3" t="n">
-        <v>22.2</v>
+        <v>24</v>
       </c>
       <c r="HO23" s="3" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="HP23" s="3" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="HQ23" s="3" t="n">
-        <v>16.7</v>
+        <v>20.2</v>
       </c>
       <c r="HR23" s="3" t="n">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="HS23" s="3" t="n">
-        <v>15.3</v>
+        <v>19</v>
       </c>
       <c r="HT23" s="3" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="HU23" s="3" t="n">
-        <v>12.3</v>
+        <v>15.4</v>
       </c>
       <c r="HV23" s="3" t="n">
-        <v>11.3</v>
+        <v>14.6</v>
       </c>
       <c r="HW23" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="HX23" s="3" t="n">
-        <v>9.1</v>
+        <v>11.5</v>
       </c>
       <c r="HY23" s="3" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="HZ23" s="3" t="n">
         <v>8</v>
@@ -20794,22 +20794,22 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CLE</t>
+          <t>SD @ ATL</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -20819,143 +20819,143 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>8.42</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>6.77</v>
+        <v>6.82</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>6.77</v>
+        <v>6.82</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>5.21</v>
+        <v>5.23</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>5.81</v>
+        <v>5.48</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5.88</v>
+        <v>5.68</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>6.66</v>
+        <v>6.51</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>5.88</v>
+        <v>5.68</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>0.883</v>
+        <v>0.873</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>8.27</v>
+        <v>7.33</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>12|8|16|3|5</t>
+          <t>10|4|2|2|12</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>12|8|16|3|5|0|21|6|5|9</t>
+          <t>10|4|2|2|12|8|5|14|0|5</t>
         </is>
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>12|8|16|3|5|0|21|6|5|9|18|0|3|11|7</t>
+          <t>10|4|2|2|12|8|5|14|0|5|0|10|5|13|20</t>
         </is>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Z24" s="5" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="AA24" s="5" t="n">
-        <v>66.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="AB24" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>61</v>
+        <v>63.5</v>
       </c>
       <c r="AD24" s="5" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="AE24" s="6" t="n">
-        <v>48.5</v>
+        <v>50.8</v>
       </c>
       <c r="AF24" s="7" t="n">
-        <v>48</v>
+        <v>50.3</v>
       </c>
       <c r="AG24" s="7" t="n">
-        <v>43.4</v>
+        <v>46.4</v>
       </c>
       <c r="AH24" s="8" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
       <c r="AI24" s="8" t="n">
-        <v>35.9</v>
+        <v>37.6</v>
       </c>
       <c r="AJ24" s="8" t="n">
-        <v>30.1</v>
+        <v>31.6</v>
       </c>
       <c r="AK24" s="8" t="n">
-        <v>29.1</v>
+        <v>30.6</v>
       </c>
       <c r="AL24" s="8" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="AM24" s="8" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="AN24" s="8" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="AO24" s="8" t="n">
-        <v>21.8</v>
+        <v>19.9</v>
       </c>
       <c r="AP24" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="AQ24" s="8" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="AR24" s="8" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="AS24" s="8" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="AT24" s="8" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="AU24" s="8" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="AV24" s="8" t="n">
-        <v>13</v>
+        <v>11.3</v>
       </c>
       <c r="AW24" s="8" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="AX24" s="8" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="AY24" s="8" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="AZ24" s="3" t="n">
-        <v>186.79</v>
+        <v>187.06</v>
       </c>
       <c r="BA24" s="4" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="BB24" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 60.0% | Edge +1.8</t>
+          <t>MORE 5.0 | 62.5% | Edge +1.8</t>
         </is>
       </c>
       <c r="BC24" s="4" t="inlineStr">
@@ -20976,21 +20976,21 @@
         <v>5</v>
       </c>
       <c r="BE24" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BF24" s="3" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="BG24" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BH24" s="4" t="inlineStr">
         <is>
-          <t>Playable</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BJ24" s="4" t="inlineStr">
         <is>
@@ -20999,14 +20999,14 @@
       </c>
       <c r="BK24" s="4" t="n"/>
       <c r="BL24" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BM24" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN24" s="4" t="inlineStr">
         <is>
-          <t>4-2-4-4-2-2-2</t>
+          <t>7-6-6-5-5-5-5</t>
         </is>
       </c>
       <c r="BO24" s="3" t="n">
@@ -21016,7 +21016,7 @@
         <v>97</v>
       </c>
       <c r="BQ24" s="3" t="n">
-        <v>5.02</v>
+        <v>4.61</v>
       </c>
       <c r="BR24" s="4" t="inlineStr">
         <is>
@@ -21024,14 +21024,14 @@
         </is>
       </c>
       <c r="BS24" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BT24" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="BU24" s="4" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Griffin Canning</t>
         </is>
       </c>
       <c r="BV24" s="4" t="inlineStr">
@@ -21040,124 +21040,124 @@
         </is>
       </c>
       <c r="BW24" s="3" t="n">
-        <v>3.85</v>
+        <v>6.67</v>
       </c>
       <c r="BX24" s="3" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="BY24" s="3" t="n">
-        <v>0.2018</v>
+        <v>0.2415</v>
       </c>
       <c r="BZ24" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.034</v>
       </c>
       <c r="CA24" s="3" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1208</v>
       </c>
       <c r="CB24" s="3" t="n">
-        <v>4.77</v>
+        <v>4.24</v>
       </c>
       <c r="CC24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="CD24" s="3" t="n">
-        <v>0.2253</v>
+        <v>0.2194</v>
       </c>
       <c r="CE24" s="3" t="n">
-        <v>0.0314</v>
+        <v>0.0292</v>
       </c>
       <c r="CF24" s="4" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="CG24" s="3" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="CH24" s="3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="CI24" s="3" t="n">
-        <v>74.2</v>
+        <v>86.3</v>
       </c>
       <c r="CJ24" s="3" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="CK24" s="3" t="n">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="CL24" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CM24" s="4" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CN24" s="3" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="CO24" s="3" t="n">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="CP24" s="3" t="n">
-        <v>0.275</v>
+        <v>0.264</v>
       </c>
       <c r="CQ24" s="3" t="n">
-        <v>0.338</v>
+        <v>0.316</v>
       </c>
       <c r="CR24" s="3" t="n">
-        <v>0.409</v>
+        <v>0.414</v>
       </c>
       <c r="CS24" s="3" t="n">
-        <v>0.747</v>
+        <v>0.73</v>
       </c>
       <c r="CT24" s="3" t="n">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="CU24" s="3" t="n">
-        <v>0.786</v>
+        <v>0.743</v>
       </c>
       <c r="CV24" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="CW24" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="CX24" s="3" t="n">
         <v>2</v>
       </c>
       <c r="CY24" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ24" s="3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="DA24" s="3" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="DB24" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="DC24" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="DD24" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="DE24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Minnesota Twins: 12 FS|2026-07-21 vs Minnesota Twins: 8 FS|2026-07-20 vs Minnesota Twins: 16 FS|2026-07-19 vs Pittsburgh Pirates: 3 FS|2026-07-18 vs Pittsburgh Pirates: 5 FS</t>
+          <t>2026-07-22 vs San Diego Padres: 10 FS|2026-07-21 vs San Diego Padres: 4 FS|2026-07-20 vs San Diego Padres: 2 FS|2026-07-19 vs Texas Rangers: 2 FS|2026-07-18 vs Texas Rangers: 12 FS</t>
         </is>
       </c>
       <c r="DF24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Minnesota Twins: 12 FS|2026-07-21 vs Minnesota Twins: 8 FS|2026-07-20 vs Minnesota Twins: 16 FS|2026-07-19 vs Pittsburgh Pirates: 3 FS|2026-07-18 vs Pittsburgh Pirates: 5 FS|2026-07-18 vs Pittsburgh Pirates: 0 FS|2026-07-12 @ Miami Marlins: 21 FS|2026-07-11 @ Miami Marlins: 6 FS|2026-07-10 @ Miami Marlins: 5 FS|2026-07-09 @ Minnesota Twins: 9 FS</t>
+          <t>2026-07-22 vs San Diego Padres: 10 FS|2026-07-21 vs San Diego Padres: 4 FS|2026-07-20 vs San Diego Padres: 2 FS|2026-07-19 vs Texas Rangers: 2 FS|2026-07-18 vs Texas Rangers: 12 FS|2026-07-17 vs Texas Rangers: 8 FS|2026-07-12 @ St. Louis Cardinals: 5 FS|2026-07-11 @ St. Louis Cardinals: 14 FS|2026-07-10 @ St. Louis Cardinals: 0 FS|2026-07-09 @ Pittsburgh Pirates: 5 FS</t>
         </is>
       </c>
       <c r="DG24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Minnesota Twins: 12 FS|2026-07-21 vs Minnesota Twins: 8 FS|2026-07-20 vs Minnesota Twins: 16 FS|2026-07-19 vs Pittsburgh Pirates: 3 FS|2026-07-18 vs Pittsburgh Pirates: 5 FS|2026-07-18 vs Pittsburgh Pirates: 0 FS|2026-07-12 @ Miami Marlins: 21 FS|2026-07-11 @ Miami Marlins: 6 FS|2026-07-10 @ Miami Marlins: 5 FS|2026-07-09 @ Minnesota Twins: 9 FS|2026-07-08 @ Minnesota Twins: 18 FS|2026-07-07 @ Minnesota Twins: 0 FS|2026-07-05 vs Chicago White Sox: 3 FS|2026-07-04 vs Chicago White Sox: 11 FS|2026-07-03 vs Chicago White Sox: 7 FS</t>
+          <t>2026-07-22 vs San Diego Padres: 10 FS|2026-07-21 vs San Diego Padres: 4 FS|2026-07-20 vs San Diego Padres: 2 FS|2026-07-19 vs Texas Rangers: 2 FS|2026-07-18 vs Texas Rangers: 12 FS|2026-07-17 vs Texas Rangers: 8 FS|2026-07-12 @ St. Louis Cardinals: 5 FS|2026-07-11 @ St. Louis Cardinals: 14 FS|2026-07-10 @ St. Louis Cardinals: 0 FS|2026-07-09 @ Pittsburgh Pirates: 5 FS|2026-07-08 @ Pittsburgh Pirates: 0 FS|2026-07-07 @ Pittsburgh Pirates: 10 FS|2026-07-06 vs New York Mets: 5 FS|2026-07-05 vs New York Mets: 13 FS|2026-07-04 vs New York Mets: 20 FS</t>
         </is>
       </c>
       <c r="DH24" s="3" t="n">
@@ -21167,7 +21167,7 @@
         <v>30</v>
       </c>
       <c r="DJ24" s="3" t="n">
-        <v>7.63</v>
+        <v>7.97</v>
       </c>
       <c r="DK24" s="3" t="n">
         <v>6.5</v>
@@ -21178,54 +21178,54 @@
         </is>
       </c>
       <c r="DM24" s="3" t="n">
-        <v>9.289999999999999</v>
+        <v>6.14</v>
       </c>
       <c r="DN24" s="3" t="n">
-        <v>8.359999999999999</v>
+        <v>6.43</v>
       </c>
       <c r="DO24" s="3" t="n">
-        <v>0.304</v>
+        <v>0.237</v>
       </c>
       <c r="DP24" s="4" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="DQ24" s="3" t="n">
-        <v>7.63</v>
+        <v>7.97</v>
       </c>
       <c r="DR24" s="3" t="n">
-        <v>2.053</v>
+        <v>1.452</v>
       </c>
       <c r="DS24" s="3" t="n">
-        <v>0.2982</v>
+        <v>0.2258</v>
       </c>
       <c r="DT24" s="3" t="n">
-        <v>0.0877</v>
+        <v>0.0806</v>
       </c>
       <c r="DU24" s="3" t="n">
-        <v>0.0526</v>
+        <v>0.0161</v>
       </c>
       <c r="DV24" s="3" t="n">
-        <v>0</v>
+        <v>0.0161</v>
       </c>
       <c r="DW24" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.0161</v>
       </c>
       <c r="DX24" s="3" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="DY24" s="3" t="n">
         <v>8.69</v>
       </c>
-      <c r="DY24" s="3" t="n">
-        <v>8.56</v>
-      </c>
       <c r="DZ24" s="3" t="n">
-        <v>8.75</v>
+        <v>7.87</v>
       </c>
       <c r="EA24" s="3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="EB24" s="3" t="n">
-        <v>7.45</v>
+        <v>7.6</v>
       </c>
       <c r="EC24" s="3" t="n">
         <v>28</v>
@@ -21243,25 +21243,25 @@
         <v>20</v>
       </c>
       <c r="EH24" s="3" t="n">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="EI24" s="3" t="n">
-        <v>81.38</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="EJ24" s="3" t="n">
-        <v>20.93</v>
+        <v>19.11</v>
       </c>
       <c r="EK24" s="3" t="n">
-        <v>0.78</v>
+        <v>0.32</v>
       </c>
       <c r="EL24" s="3" t="n">
-        <v>32.17</v>
+        <v>31.21</v>
       </c>
       <c r="EM24" s="3" t="n">
-        <v>0.315</v>
+        <v>0.34</v>
       </c>
       <c r="EN24" s="3" t="n">
-        <v>0.8256</v>
+        <v>0.8218</v>
       </c>
       <c r="EO24" s="3" t="n">
         <v>1</v>
@@ -21273,10 +21273,10 @@
         <v>1</v>
       </c>
       <c r="ER24" s="3" t="n">
-        <v>0.9628</v>
+        <v>1.0107</v>
       </c>
       <c r="ES24" s="3" t="n">
-        <v>339</v>
+        <v>600</v>
       </c>
       <c r="ET24" s="4" t="inlineStr">
         <is>
@@ -21284,63 +21284,63 @@
         </is>
       </c>
       <c r="EU24" s="3" t="n">
-        <v>1.069</v>
+        <v>1</v>
       </c>
       <c r="EV24" s="3" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="EW24" s="4" t="inlineStr">
         <is>
-          <t>Statcast</t>
+          <t>Fallback</t>
         </is>
       </c>
       <c r="EX24" s="3" t="n">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="EY24" s="3" t="n">
-        <v>81.38</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="EZ24" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FA24" s="3" t="n">
-        <v>17.53</v>
+        <v>22.14</v>
       </c>
       <c r="FB24" s="3" t="n">
-        <v>33.61</v>
+        <v>31.36</v>
       </c>
       <c r="FC24" s="3" t="n">
-        <v>14.3</v>
+        <v>15.9</v>
       </c>
       <c r="FD24" s="3" t="n">
-        <v>58.9</v>
+        <v>67.2</v>
       </c>
       <c r="FE24" s="3" t="n">
-        <v>26.7</v>
+        <v>16.9</v>
       </c>
       <c r="FF24" s="3" t="n">
-        <v>0.9761</v>
+        <v>1.0307</v>
       </c>
       <c r="FG24" s="3" t="n">
-        <v>0.9943</v>
+        <v>0.9933</v>
       </c>
       <c r="FH24" s="3" t="n">
-        <v>0.9559</v>
+        <v>1.0054</v>
       </c>
       <c r="FI24" s="3" t="n">
-        <v>0.9887</v>
+        <v>0.9866</v>
       </c>
       <c r="FJ24" s="3" t="n">
-        <v>0.9393</v>
+        <v>0.9847</v>
       </c>
       <c r="FK24" s="3" t="n">
-        <v>1.0115</v>
+        <v>0.9873</v>
       </c>
       <c r="FL24" s="3" t="n">
-        <v>8.59</v>
+        <v>6.91</v>
       </c>
       <c r="FM24" s="3" t="n">
-        <v>0.95</v>
+        <v>-1.06</v>
       </c>
       <c r="FN24" s="4" t="inlineStr">
         <is>
@@ -21385,52 +21385,52 @@
         <v>27</v>
       </c>
       <c r="FZ24" s="3" t="n">
-        <v>1.3</v>
+        <v>0.9916</v>
       </c>
       <c r="GA24" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GB24" s="3" t="n">
-        <v>0.9954</v>
+        <v>1</v>
       </c>
       <c r="GC24" s="3" t="n">
-        <v>0.1503</v>
+        <v>0.1535</v>
       </c>
       <c r="GD24" s="3" t="n">
-        <v>0.0321</v>
+        <v>0.048</v>
       </c>
       <c r="GE24" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.0041</v>
       </c>
       <c r="GF24" s="3" t="n">
-        <v>0.0258</v>
+        <v>0.0244</v>
       </c>
       <c r="GG24" s="3" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="GH24" s="3" t="n">
-        <v>0.0124</v>
+        <v>0.0101</v>
       </c>
       <c r="GI24" s="3" t="n">
-        <v>0.1822</v>
+        <v>0.174</v>
       </c>
       <c r="GJ24" s="3" t="n">
-        <v>0.4015</v>
+        <v>0.4927</v>
       </c>
       <c r="GK24" s="3" t="n">
-        <v>0.2879</v>
+        <v>0.2536</v>
       </c>
       <c r="GL24" s="3" t="n">
-        <v>0.3106</v>
+        <v>0.2536</v>
       </c>
       <c r="GM24" s="3" t="n">
-        <v>0.1217</v>
+        <v>0.122</v>
       </c>
       <c r="GN24" s="3" t="n">
-        <v>0.1285</v>
+        <v>0.1416</v>
       </c>
       <c r="GO24" s="3" t="n">
-        <v>0.0211</v>
+        <v>0.0117</v>
       </c>
       <c r="GP24" s="3" t="n">
         <v>1</v>
@@ -21441,19 +21441,19 @@
         </is>
       </c>
       <c r="GR24" s="3" t="n">
-        <v>5.88</v>
+        <v>5.68</v>
       </c>
       <c r="GS24" s="3" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="GT24" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="GU24" s="3" t="n">
-        <v>14.92</v>
+        <v>14.83</v>
       </c>
       <c r="GV24" s="3" t="n">
-        <v>4.67</v>
+        <v>4.23</v>
       </c>
       <c r="GW24" s="3" t="n">
         <v>0</v>
@@ -21464,88 +21464,88 @@
         </is>
       </c>
       <c r="GY24" s="3" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="GZ24" s="3" t="n">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="HA24" s="3" t="n">
-        <v>59.1</v>
+        <v>62</v>
       </c>
       <c r="HB24" s="3" t="n">
-        <v>59.1</v>
+        <v>62</v>
       </c>
       <c r="HC24" s="3" t="n">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="HD24" s="3" t="n">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="HE24" s="3" t="n">
-        <v>44</v>
+        <v>46.3</v>
       </c>
       <c r="HF24" s="3" t="n">
-        <v>44</v>
+        <v>46.3</v>
       </c>
       <c r="HG24" s="3" t="n">
-        <v>39.9</v>
+        <v>42.9</v>
       </c>
       <c r="HH24" s="3" t="n">
-        <v>33.4</v>
+        <v>35.1</v>
       </c>
       <c r="HI24" s="3" t="n">
-        <v>33.4</v>
+        <v>35.1</v>
       </c>
       <c r="HJ24" s="3" t="n">
-        <v>29.1</v>
+        <v>30.6</v>
       </c>
       <c r="HK24" s="3" t="n">
-        <v>29.1</v>
+        <v>30.6</v>
       </c>
       <c r="HL24" s="3" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="HM24" s="3" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="HN24" s="3" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="HO24" s="3" t="n">
-        <v>21.8</v>
+        <v>19.9</v>
       </c>
       <c r="HP24" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="HQ24" s="3" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="HR24" s="3" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="HS24" s="3" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="HT24" s="3" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="HU24" s="3" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="HV24" s="3" t="n">
-        <v>13</v>
+        <v>11.3</v>
       </c>
       <c r="HW24" s="3" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="HX24" s="3" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="HY24" s="3" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="HZ24" s="3" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="IA24" s="3" t="n">
         <v>8</v>
@@ -21930,13 +21930,13 @@
         <v>1.03</v>
       </c>
       <c r="CI25" s="3" t="n">
-        <v>85.2</v>
+        <v>86.3</v>
       </c>
       <c r="CJ25" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="CK25" s="3" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="CL25" s="3" t="n">
         <v>3</v>
@@ -22527,13 +22527,13 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.15</v>
+        <v>8.16</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6.83</v>
+        <v>6.84</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>6.83</v>
+        <v>6.84</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>5.32</v>
@@ -22545,13 +22545,13 @@
         <v>4.84</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5.86</v>
+        <v>5.84</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>4.84</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>9.800000000000001</v>
@@ -22578,67 +22578,67 @@
         </is>
       </c>
       <c r="Y26" s="5" t="n">
-        <v>91.3</v>
+        <v>91.5</v>
       </c>
       <c r="Z26" s="5" t="n">
-        <v>84</v>
+        <v>84.2</v>
       </c>
       <c r="AA26" s="5" t="n">
-        <v>83.5</v>
+        <v>83.7</v>
       </c>
       <c r="AB26" s="5" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
       <c r="AD26" s="5" t="n">
-        <v>65.5</v>
+        <v>65.7</v>
       </c>
       <c r="AE26" s="6" t="n">
-        <v>53.4</v>
+        <v>53.8</v>
       </c>
       <c r="AF26" s="7" t="n">
-        <v>52.9</v>
+        <v>53.3</v>
       </c>
       <c r="AG26" s="7" t="n">
-        <v>47.3</v>
+        <v>47.7</v>
       </c>
       <c r="AH26" s="8" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="AI26" s="8" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="AJ26" s="8" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="AK26" s="8" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="AL26" s="8" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="AM26" s="8" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AN26" s="8" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AO26" s="8" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AP26" s="8" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AQ26" s="8" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="AR26" s="8" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="AS26" s="8" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="AT26" s="8" t="n">
         <v>10.3</v>
@@ -22647,19 +22647,19 @@
         <v>10.3</v>
       </c>
       <c r="AV26" s="8" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW26" s="8" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX26" s="8" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY26" s="8" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AZ26" s="3" t="n">
-        <v>185.86</v>
+        <v>186.08</v>
       </c>
       <c r="BA26" s="4" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
       </c>
       <c r="BB26" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 65.5% | Edge +1.8</t>
+          <t>MORE 5.0 | 65.7% | Edge +1.8</t>
         </is>
       </c>
       <c r="BC26" s="4" t="inlineStr">
@@ -22680,13 +22680,13 @@
         <v>5</v>
       </c>
       <c r="BE26" s="3" t="n">
-        <v>65.5</v>
+        <v>65.7</v>
       </c>
       <c r="BF26" s="3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BG26" s="3" t="n">
-        <v>31</v>
+        <v>31.4</v>
       </c>
       <c r="BH26" s="4" t="inlineStr">
         <is>
@@ -22782,13 +22782,13 @@
         <v>1</v>
       </c>
       <c r="CI26" s="3" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="CJ26" s="3" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CK26" s="3" t="n">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="CL26" s="3" t="n">
         <v>0</v>
@@ -22923,7 +22923,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="DZ26" s="3" t="n">
-        <v>9.27</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="EA26" s="3" t="n">
         <v>9.16</v>
@@ -23023,19 +23023,19 @@
         <v>15.2</v>
       </c>
       <c r="FF26" s="3" t="n">
-        <v>0.9757</v>
+        <v>0.9777</v>
       </c>
       <c r="FG26" s="3" t="n">
         <v>0.9886</v>
       </c>
       <c r="FH26" s="3" t="n">
-        <v>0.9348</v>
+        <v>0.9367</v>
       </c>
       <c r="FI26" s="3" t="n">
         <v>0.9771</v>
       </c>
       <c r="FJ26" s="3" t="n">
-        <v>0.9013</v>
+        <v>0.9031</v>
       </c>
       <c r="FK26" s="3" t="n">
         <v>1.0252</v>
@@ -23101,13 +23101,13 @@
         <v>0.1605</v>
       </c>
       <c r="GD26" s="3" t="n">
-        <v>0.0331</v>
+        <v>0.0332</v>
       </c>
       <c r="GE26" s="3" t="n">
         <v>0.0049</v>
       </c>
       <c r="GF26" s="3" t="n">
-        <v>0.0148</v>
+        <v>0.0149</v>
       </c>
       <c r="GG26" s="3" t="n">
         <v>0.1217</v>
@@ -23148,13 +23148,13 @@
         <v>4.84</v>
       </c>
       <c r="GS26" s="3" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="GT26" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="GU26" s="3" t="n">
-        <v>13.58</v>
+        <v>13.6</v>
       </c>
       <c r="GV26" s="3" t="n">
         <v>4.76</v>
@@ -23168,67 +23168,67 @@
         </is>
       </c>
       <c r="GY26" s="3" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="GZ26" s="3" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="HA26" s="3" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="HB26" s="3" t="n">
-        <v>66.3</v>
+        <v>66</v>
       </c>
       <c r="HC26" s="3" t="n">
-        <v>60.5</v>
+        <v>60.7</v>
       </c>
       <c r="HD26" s="3" t="n">
-        <v>60.5</v>
+        <v>60.7</v>
       </c>
       <c r="HE26" s="3" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="HF26" s="3" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="HG26" s="3" t="n">
-        <v>43.8</v>
+        <v>44.2</v>
       </c>
       <c r="HH26" s="3" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="HI26" s="3" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="HJ26" s="3" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="HK26" s="3" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="HL26" s="3" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="HM26" s="3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="HN26" s="3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="HO26" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="HP26" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="HQ26" s="3" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="HR26" s="3" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="HS26" s="3" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="HT26" s="3" t="n">
         <v>10.3</v>
@@ -23237,19 +23237,19 @@
         <v>10.3</v>
       </c>
       <c r="HV26" s="3" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="HW26" s="3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="HX26" s="3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="HY26" s="3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="HZ26" s="3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="IA26" s="3" t="n">
         <v>8</v>
@@ -23382,10 +23382,10 @@
         <v>7.99</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.67</v>
+        <v>6.66</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>6.67</v>
+        <v>6.66</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>5.02</v>
@@ -23397,13 +23397,13 @@
         <v>7.04</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>7.04</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.986</v>
+        <v>0.989</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>12.8</v>
@@ -23448,19 +23448,19 @@
         <v>55.4</v>
       </c>
       <c r="AE27" s="7" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="AF27" s="7" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="AG27" s="7" t="n">
         <v>41.1</v>
       </c>
       <c r="AH27" s="8" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="AI27" s="8" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="AJ27" s="8" t="n">
         <v>29.3</v>
@@ -23481,37 +23481,37 @@
         <v>22.5</v>
       </c>
       <c r="AP27" s="8" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AQ27" s="8" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AR27" s="8" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AS27" s="8" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AT27" s="8" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AU27" s="8" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AV27" s="8" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="AW27" s="8" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="AX27" s="8" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="AY27" s="8" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="AZ27" s="3" t="n">
-        <v>184.73</v>
+        <v>184.58</v>
       </c>
       <c r="BA27" s="4" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>63.6</v>
       </c>
       <c r="BF27" s="3" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="BG27" s="3" t="n">
         <v>27.2</v>
@@ -24000,13 +24000,13 @@
         <v>7.04</v>
       </c>
       <c r="GS27" s="3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="GT27" s="3" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="GU27" s="3" t="n">
-        <v>17.84</v>
+        <v>17.88</v>
       </c>
       <c r="GV27" s="3" t="n">
         <v>4.11</v>
@@ -24038,19 +24038,19 @@
         <v>50.4</v>
       </c>
       <c r="HE27" s="3" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="HF27" s="3" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="HG27" s="3" t="n">
         <v>37.6</v>
       </c>
       <c r="HH27" s="3" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="HI27" s="3" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="HJ27" s="3" t="n">
         <v>28.3</v>
@@ -24071,34 +24071,34 @@
         <v>22.5</v>
       </c>
       <c r="HP27" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="HQ27" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="HR27" s="3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="HS27" s="3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="HT27" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="HU27" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="HV27" s="3" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="HW27" s="3" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="HX27" s="3" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="HY27" s="3" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="HZ27" s="3" t="n">
         <v>8</v>
@@ -24234,13 +24234,13 @@
         <v>7.33</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>7.33</v>
+        <v>7.34</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>7.33</v>
+        <v>7.34</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>7.55</v>
@@ -24249,13 +24249,13 @@
         <v>7.01</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>7.17</v>
+        <v>7.19</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>7.01</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.977</v>
+        <v>0.975</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>5</v>
@@ -24282,10 +24282,10 @@
         </is>
       </c>
       <c r="Y28" s="5" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Z28" s="5" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AA28" s="5" t="n">
         <v>69.8</v>
@@ -24300,10 +24300,10 @@
         <v>62.3</v>
       </c>
       <c r="AE28" s="6" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="AF28" s="7" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="AG28" s="7" t="n">
         <v>46.3</v>
@@ -24312,7 +24312,7 @@
         <v>45.8</v>
       </c>
       <c r="AI28" s="8" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="AJ28" s="8" t="n">
         <v>32.8</v>
@@ -24327,10 +24327,10 @@
         <v>28</v>
       </c>
       <c r="AN28" s="8" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AO28" s="8" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AP28" s="8" t="n">
         <v>22.6</v>
@@ -24345,25 +24345,25 @@
         <v>20.1</v>
       </c>
       <c r="AT28" s="8" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AU28" s="8" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AV28" s="8" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="AW28" s="8" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="AX28" s="8" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="AY28" s="8" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="AZ28" s="3" t="n">
-        <v>182.02</v>
+        <v>182.15</v>
       </c>
       <c r="BA28" s="4" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>62.3</v>
       </c>
       <c r="BF28" s="3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="BG28" s="3" t="n">
         <v>24.6</v>
@@ -24852,13 +24852,13 @@
         <v>7.01</v>
       </c>
       <c r="GS28" s="3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="GT28" s="3" t="n">
-        <v>9.94</v>
+        <v>9.93</v>
       </c>
       <c r="GU28" s="3" t="n">
-        <v>17.76</v>
+        <v>17.73</v>
       </c>
       <c r="GV28" s="3" t="n">
         <v>4.34</v>
@@ -24872,10 +24872,10 @@
         </is>
       </c>
       <c r="GY28" s="3" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="GZ28" s="3" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="HA28" s="3" t="n">
         <v>62.3</v>
@@ -24890,10 +24890,10 @@
         <v>57.3</v>
       </c>
       <c r="HE28" s="3" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="HF28" s="3" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="HG28" s="3" t="n">
         <v>42.8</v>
@@ -24902,7 +24902,7 @@
         <v>42.8</v>
       </c>
       <c r="HI28" s="3" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="HJ28" s="3" t="n">
         <v>31.8</v>
@@ -24917,10 +24917,10 @@
         <v>28</v>
       </c>
       <c r="HN28" s="3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="HO28" s="3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="HP28" s="3" t="n">
         <v>22.6</v>
@@ -24935,22 +24935,22 @@
         <v>20.1</v>
       </c>
       <c r="HT28" s="3" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="HU28" s="3" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="HV28" s="3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="HW28" s="3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="HX28" s="3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="HY28" s="3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="HZ28" s="3" t="n">
         <v>8</v>
@@ -25101,13 +25101,13 @@
         <v>6.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>6.3</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.915</v>
+        <v>0.914</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>10.2</v>
@@ -25134,22 +25134,22 @@
         </is>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Z29" s="5" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AA29" s="5" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="AB29" s="5" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="AD29" s="5" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="AE29" s="6" t="n">
         <v>46.4</v>
@@ -25167,22 +25167,22 @@
         <v>35.3</v>
       </c>
       <c r="AJ29" s="8" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="AL29" s="8" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="AM29" s="8" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="AN29" s="8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AO29" s="8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AP29" s="8" t="n">
         <v>20.7</v>
@@ -25215,7 +25215,7 @@
         <v>10.6</v>
       </c>
       <c r="AZ29" s="3" t="n">
-        <v>177.41</v>
+        <v>177.42</v>
       </c>
       <c r="BA29" s="4" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
       </c>
       <c r="BB29" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 58.2% | Edge +1.6</t>
+          <t>MORE 5.0 | 58.1% | Edge +1.6</t>
         </is>
       </c>
       <c r="BC29" s="4" t="inlineStr">
@@ -25236,13 +25236,13 @@
         <v>5</v>
       </c>
       <c r="BE29" s="3" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="BF29" s="3" t="n">
         <v>1.63</v>
       </c>
       <c r="BG29" s="3" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="BH29" s="4" t="inlineStr">
         <is>
@@ -25704,13 +25704,13 @@
         <v>6.3</v>
       </c>
       <c r="GS29" s="3" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="GT29" s="3" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="GU29" s="3" t="n">
-        <v>16.12</v>
+        <v>16.11</v>
       </c>
       <c r="GV29" s="3" t="n">
         <v>4.41</v>
@@ -25724,22 +25724,22 @@
         </is>
       </c>
       <c r="GY29" s="3" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="GZ29" s="3" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="HA29" s="3" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="HB29" s="3" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="HC29" s="3" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="HD29" s="3" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="HE29" s="3" t="n">
         <v>41.9</v>
@@ -25757,22 +25757,22 @@
         <v>32.8</v>
       </c>
       <c r="HJ29" s="3" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="HK29" s="3" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="HL29" s="3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="HM29" s="3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="HN29" s="3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="HO29" s="3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="HP29" s="3" t="n">
         <v>20.7</v>
@@ -25938,10 +25938,10 @@
         <v>7.98</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>5.22</v>
@@ -25953,13 +25953,13 @@
         <v>4.93</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>6.04</v>
+        <v>6.03</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>4.93</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>9.6</v>
@@ -25989,13 +25989,13 @@
         <v>87.59999999999999</v>
       </c>
       <c r="Z30" s="5" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AA30" s="5" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AB30" s="5" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AC30" s="5" t="n">
         <v>59.8</v>
@@ -26010,7 +26010,7 @@
         <v>45.9</v>
       </c>
       <c r="AG30" s="7" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="AH30" s="8" t="n">
         <v>33.4</v>
@@ -26019,7 +26019,7 @@
         <v>32.9</v>
       </c>
       <c r="AJ30" s="8" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>22.6</v>
@@ -26052,10 +26052,10 @@
         <v>9.9</v>
       </c>
       <c r="AU30" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV30" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW30" s="8" t="n">
         <v>7.2</v>
@@ -26067,7 +26067,7 @@
         <v>6.1</v>
       </c>
       <c r="AZ30" s="3" t="n">
-        <v>176.03</v>
+        <v>175.88</v>
       </c>
       <c r="BA30" s="4" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>58.8</v>
       </c>
       <c r="BF30" s="3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BG30" s="3" t="n">
         <v>17.6</v>
@@ -26556,13 +26556,13 @@
         <v>4.93</v>
       </c>
       <c r="GS30" s="3" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="GT30" s="3" t="n">
         <v>8.49</v>
       </c>
       <c r="GU30" s="3" t="n">
-        <v>12.57</v>
+        <v>12.58</v>
       </c>
       <c r="GV30" s="3" t="n">
         <v>4.14</v>
@@ -26579,13 +26579,13 @@
         <v>79.59999999999999</v>
       </c>
       <c r="GZ30" s="3" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="HA30" s="3" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="HB30" s="3" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="HC30" s="3" t="n">
         <v>53.8</v>
@@ -26600,7 +26600,7 @@
         <v>41.9</v>
       </c>
       <c r="HG30" s="3" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="HH30" s="3" t="n">
         <v>30.4</v>
@@ -26609,7 +26609,7 @@
         <v>30.4</v>
       </c>
       <c r="HJ30" s="3" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="HK30" s="3" t="n">
         <v>22.6</v>
@@ -26642,10 +26642,10 @@
         <v>9.9</v>
       </c>
       <c r="HU30" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="HV30" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="HW30" s="3" t="n">
         <v>7.2</v>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Z31" s="6" t="n">
         <v>57.1</v>
@@ -26847,10 +26847,10 @@
         <v>56.6</v>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="AC31" s="7" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>39.5</v>
@@ -26886,10 +26886,10 @@
         <v>19.7</v>
       </c>
       <c r="AO31" s="8" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="AP31" s="8" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="AQ31" s="8" t="n">
         <v>16.1</v>
@@ -26928,7 +26928,7 @@
       </c>
       <c r="BB31" s="9" t="inlineStr">
         <is>
-          <t>MORE 2.5 | 68.8% | Edge +3.1</t>
+          <t>MORE 2.5 | 68.9% | Edge +3.1</t>
         </is>
       </c>
       <c r="BC31" s="4" t="inlineStr">
@@ -26940,13 +26940,13 @@
         <v>2.5</v>
       </c>
       <c r="BE31" s="3" t="n">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="BF31" s="3" t="n">
         <v>3.07</v>
       </c>
       <c r="BG31" s="3" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="BH31" s="4" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         </is>
       </c>
       <c r="GY31" s="3" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="GZ31" s="3" t="n">
         <v>49.1</v>
@@ -27437,10 +27437,10 @@
         <v>49.1</v>
       </c>
       <c r="HB31" s="3" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="HC31" s="3" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="HD31" s="3" t="n">
         <v>34.5</v>
@@ -27476,10 +27476,10 @@
         <v>19.7</v>
       </c>
       <c r="HO31" s="3" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="HP31" s="3" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="HQ31" s="3" t="n">
         <v>16.1</v>
